--- a/AlphaARC_BugReport.xlsx
+++ b/AlphaARC_BugReport.xlsx
@@ -58,40 +58,40 @@
     <t>Bug-006</t>
   </si>
   <si>
+    <t>If the user attempts to delete a habit while the internet connection is unavailable, the habit disappears from the UI even though the delete request cannot be completed.</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Bug-007</t>
+  </si>
+  <si>
     <t>Habit completion fails on slow internet connection</t>
   </si>
   <si>
-    <t>Bug-007</t>
+    <t>Bug-008</t>
   </si>
   <si>
     <t>When multiple habits exist and one completed habit is deleted, the daily completion state does not update until another habit is created or an existing habit is toggled again.</t>
   </si>
   <si>
-    <t>Bug-008</t>
+    <t>Bug-009</t>
   </si>
   <si>
     <t>create and edit --- Habit remains in updating state after internet connection is restored</t>
   </si>
   <si>
-    <t>Bug-009</t>
+    <t>Bug-010</t>
   </si>
   <si>
     <t>Questions are not aligned with the step numbers in the Streak Instructions screen</t>
   </si>
   <si>
-    <t>Bug-010</t>
-  </si>
-  <si>
-    <t>If the user attempts to delete a habit while the internet connection is unavailable, the habit disappears from the UI even though the delete request cannot be completed.</t>
-  </si>
-  <si>
     <t>Bug-011</t>
   </si>
   <si>
     <t>OTP resend timer (30 seconds) stops after clicking resend code</t>
-  </si>
-  <si>
-    <t>Done</t>
   </si>
   <si>
     <t>Bug-012</t>
@@ -4311,7 +4311,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -4329,6 +4329,10 @@
     </font>
     <font>
       <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <color rgb="FFD4EDBC"/>
       <name val="Roboto"/>
     </font>
     <font>
@@ -4376,7 +4380,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -4401,6 +4405,12 @@
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -4409,9 +4419,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4800,66 +4807,89 @@
       <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>5</v>
-      </c>
+      <c r="C7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="C8" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="7" t="s">
         <v>19</v>
       </c>
+      <c r="B9" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="C9" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="B10" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="C10" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="7" t="s">
         <v>23</v>
       </c>
+      <c r="B11" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C11" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
@@ -4870,7 +4900,7 @@
         <v>28</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
@@ -4881,7 +4911,7 @@
         <v>30</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
@@ -4892,7 +4922,7 @@
         <v>32</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
@@ -4903,7 +4933,7 @@
         <v>34</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
@@ -4914,7 +4944,7 @@
         <v>36</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
@@ -4925,7 +4955,7 @@
         <v>38</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
@@ -4936,7 +4966,7 @@
         <v>40</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
@@ -4947,7 +4977,7 @@
         <v>42</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
@@ -4958,7 +4988,7 @@
         <v>44</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
@@ -4969,7 +4999,7 @@
         <v>46</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
@@ -4980,7 +5010,7 @@
         <v>48</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
@@ -4991,7 +5021,7 @@
         <v>50</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
@@ -5002,7 +5032,7 @@
         <v>52</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
@@ -5013,7 +5043,7 @@
         <v>54</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
@@ -5024,7 +5054,7 @@
         <v>56</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
@@ -5035,7 +5065,7 @@
         <v>58</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
@@ -5046,7 +5076,7 @@
         <v>60</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" ht="22.5" customHeight="1">
@@ -5057,7 +5087,7 @@
         <v>62</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
@@ -5068,7 +5098,7 @@
         <v>64</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
@@ -5079,7 +5109,7 @@
         <v>66</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
@@ -5090,7 +5120,7 @@
         <v>68</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
@@ -5101,7 +5131,7 @@
         <v>70</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
@@ -5112,7 +5142,7 @@
         <v>72</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" ht="22.5" customHeight="1">
@@ -5123,7 +5153,7 @@
         <v>74</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
@@ -5134,7 +5164,7 @@
         <v>76</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" ht="22.5" customHeight="1">
@@ -5145,7 +5175,7 @@
         <v>78</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" ht="22.5" customHeight="1">
@@ -5156,7 +5186,7 @@
         <v>80</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" ht="22.5" customHeight="1">
@@ -5167,7 +5197,7 @@
         <v>82</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" ht="22.5" customHeight="1">
@@ -5178,7 +5208,7 @@
         <v>84</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
@@ -5189,7 +5219,7 @@
         <v>86</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
@@ -5200,7 +5230,7 @@
         <v>88</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" ht="22.5" customHeight="1">
@@ -5211,7 +5241,7 @@
         <v>90</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
@@ -5222,7 +5252,7 @@
         <v>92</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
@@ -5233,7 +5263,7 @@
         <v>94</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" ht="22.5" customHeight="1">
@@ -5244,7 +5274,7 @@
         <v>96</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
@@ -5255,7 +5285,7 @@
         <v>98</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
@@ -5266,7 +5296,7 @@
         <v>100</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
@@ -5277,7 +5307,7 @@
         <v>102</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
@@ -5288,7 +5318,7 @@
         <v>104</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
@@ -5299,7 +5329,7 @@
         <v>106</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" ht="22.5" customHeight="1">
@@ -5310,7 +5340,7 @@
         <v>108</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" ht="22.5" customHeight="1">
@@ -5321,7 +5351,7 @@
         <v>110</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" ht="22.5" customHeight="1">
@@ -5332,7 +5362,7 @@
         <v>112</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" ht="22.5" customHeight="1">
@@ -5343,7 +5373,7 @@
         <v>114</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" ht="22.5" customHeight="1">
@@ -5354,7 +5384,7 @@
         <v>116</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
@@ -5365,7 +5395,7 @@
         <v>118</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" ht="22.5" customHeight="1">
@@ -5376,7 +5406,7 @@
         <v>120</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
@@ -5387,7 +5417,7 @@
         <v>122</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" ht="22.5" customHeight="1">
@@ -5398,7 +5428,7 @@
         <v>124</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" ht="22.5" customHeight="1">
@@ -5409,7 +5439,7 @@
         <v>126</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
@@ -5420,7 +5450,7 @@
         <v>128</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
@@ -5431,7 +5461,7 @@
         <v>130</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
@@ -5442,7 +5472,7 @@
         <v>132</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
@@ -5453,7 +5483,7 @@
         <v>134</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1">
@@ -5464,7 +5494,7 @@
         <v>136</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" ht="22.5" customHeight="1">
@@ -5475,7 +5505,7 @@
         <v>138</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1">
@@ -5486,7 +5516,7 @@
         <v>140</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" ht="22.5" customHeight="1">
@@ -5497,7 +5527,7 @@
         <v>142</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" ht="22.5" customHeight="1">
@@ -5508,7 +5538,7 @@
         <v>144</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" ht="22.5" customHeight="1">
@@ -5519,7 +5549,7 @@
         <v>146</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73" ht="22.5" customHeight="1">
@@ -5530,7 +5560,7 @@
         <v>148</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" ht="22.5" customHeight="1">
@@ -5541,7 +5571,7 @@
         <v>150</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1">
@@ -5552,7 +5582,7 @@
         <v>152</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1">
@@ -5563,7 +5593,7 @@
         <v>154</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" ht="22.5" customHeight="1">
@@ -5574,7 +5604,7 @@
         <v>156</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" ht="22.5" customHeight="1">
@@ -5585,7 +5615,7 @@
         <v>158</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" ht="22.5" customHeight="1">
@@ -5596,7 +5626,7 @@
         <v>160</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
@@ -5607,7 +5637,7 @@
         <v>162</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" ht="22.5" customHeight="1">
@@ -5618,7 +5648,7 @@
         <v>164</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82" ht="22.5" customHeight="1">
@@ -5629,7 +5659,7 @@
         <v>166</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" ht="22.5" customHeight="1">
@@ -5640,7 +5670,7 @@
         <v>168</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" ht="22.5" customHeight="1">
@@ -5651,7 +5681,7 @@
         <v>170</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85" ht="22.5" customHeight="1">
@@ -5662,7 +5692,7 @@
         <v>172</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
@@ -5673,7 +5703,7 @@
         <v>174</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87" ht="22.5" customHeight="1">
@@ -5684,7 +5714,7 @@
         <v>176</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
@@ -5695,7 +5725,7 @@
         <v>178</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89" ht="22.5" customHeight="1">
@@ -5706,7 +5736,7 @@
         <v>180</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
@@ -5717,7 +5747,7 @@
         <v>182</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
@@ -5728,7 +5758,7 @@
         <v>184</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" ht="22.5" customHeight="1">
@@ -5739,7 +5769,7 @@
         <v>186</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" ht="22.5" customHeight="1">
@@ -5750,7 +5780,7 @@
         <v>188</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94" ht="22.5" customHeight="1">
@@ -5761,7 +5791,7 @@
         <v>190</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" ht="22.5" customHeight="1">
@@ -5772,7 +5802,7 @@
         <v>192</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
@@ -5783,7 +5813,7 @@
         <v>194</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97" ht="22.5" customHeight="1">
@@ -5794,7 +5824,7 @@
         <v>196</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" ht="22.5" customHeight="1">
@@ -5805,7 +5835,7 @@
         <v>198</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" ht="22.5" customHeight="1">
@@ -5816,7 +5846,7 @@
         <v>200</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" ht="22.5" customHeight="1">
@@ -5827,7 +5857,7 @@
         <v>202</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" ht="22.5" customHeight="1">
@@ -5838,7 +5868,7 @@
         <v>204</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" ht="22.5" customHeight="1">
@@ -5849,7 +5879,7 @@
         <v>206</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" ht="22.5" customHeight="1">
@@ -5860,7 +5890,7 @@
         <v>208</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" ht="22.5" customHeight="1">
@@ -5871,7 +5901,7 @@
         <v>210</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" ht="22.5" customHeight="1">
@@ -5882,7 +5912,7 @@
         <v>212</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106" ht="22.5" customHeight="1">
@@ -5893,7 +5923,7 @@
         <v>214</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" ht="22.5" customHeight="1">
@@ -5904,7 +5934,7 @@
         <v>216</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108" ht="22.5" customHeight="1">
@@ -5915,7 +5945,7 @@
         <v>218</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109" ht="22.5" customHeight="1">
@@ -5926,7 +5956,7 @@
         <v>220</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="110" ht="22.5" customHeight="1">
@@ -5937,7 +5967,7 @@
         <v>222</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111" ht="22.5" customHeight="1">
@@ -5948,7 +5978,7 @@
         <v>224</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" ht="22.5" customHeight="1">
@@ -5959,7 +5989,7 @@
         <v>226</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" ht="22.5" customHeight="1">
@@ -5970,7 +6000,7 @@
         <v>228</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114" ht="22.5" customHeight="1">
@@ -5981,7 +6011,7 @@
         <v>230</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="115" ht="22.5" customHeight="1">
@@ -5992,7 +6022,7 @@
         <v>232</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="116" ht="22.5" customHeight="1">
@@ -6003,7 +6033,7 @@
         <v>234</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" ht="22.5" customHeight="1">
@@ -6014,7 +6044,7 @@
         <v>236</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118" ht="22.5" customHeight="1">
@@ -6025,7 +6055,7 @@
         <v>238</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119" ht="22.5" customHeight="1">
@@ -6036,7 +6066,7 @@
         <v>240</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120" ht="22.5" customHeight="1">
@@ -6047,7 +6077,7 @@
         <v>242</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="121" ht="22.5" customHeight="1">
@@ -6058,7 +6088,7 @@
         <v>244</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="122" ht="22.5" customHeight="1">
@@ -6069,7 +6099,7 @@
         <v>246</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" ht="22.5" customHeight="1">
@@ -6080,7 +6110,7 @@
         <v>248</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="124" ht="22.5" customHeight="1">
@@ -6091,7 +6121,7 @@
         <v>250</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125" ht="22.5" customHeight="1">
@@ -6102,7 +6132,7 @@
         <v>252</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="126" ht="22.5" customHeight="1">
@@ -6113,7 +6143,7 @@
         <v>254</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127" ht="22.5" customHeight="1">
@@ -6124,7 +6154,7 @@
         <v>256</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128" ht="22.5" customHeight="1">
@@ -6135,7 +6165,7 @@
         <v>258</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" ht="22.5" customHeight="1">
@@ -6146,7 +6176,7 @@
         <v>260</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="130" ht="22.5" customHeight="1">
@@ -6157,7 +6187,7 @@
         <v>262</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="131" ht="22.5" customHeight="1">
@@ -6168,7 +6198,7 @@
         <v>264</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="132" ht="22.5" customHeight="1">
@@ -6179,7 +6209,7 @@
         <v>266</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="133" ht="22.5" customHeight="1">
@@ -6190,7 +6220,7 @@
         <v>268</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134" ht="22.5" customHeight="1">
@@ -6201,7 +6231,7 @@
         <v>270</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" ht="22.5" customHeight="1">
@@ -6212,7 +6242,7 @@
         <v>272</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" ht="22.5" customHeight="1">
@@ -6223,7 +6253,7 @@
         <v>274</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137" ht="22.5" customHeight="1">
@@ -6234,7 +6264,7 @@
         <v>276</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138" ht="22.5" customHeight="1">
@@ -6245,7 +6275,7 @@
         <v>278</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139" ht="22.5" customHeight="1">
@@ -6256,7 +6286,7 @@
         <v>280</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="140" ht="22.5" customHeight="1">
@@ -6267,7 +6297,7 @@
         <v>282</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="141" ht="22.5" customHeight="1">
@@ -6278,7 +6308,7 @@
         <v>284</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="142" ht="22.5" customHeight="1">
@@ -6289,7 +6319,7 @@
         <v>286</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="143" ht="22.5" customHeight="1">
@@ -6300,7 +6330,7 @@
         <v>288</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="144" ht="22.5" customHeight="1">
@@ -6311,7 +6341,7 @@
         <v>290</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="145" ht="22.5" customHeight="1">
@@ -6322,7 +6352,7 @@
         <v>292</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="146" ht="22.5" customHeight="1">
@@ -6333,7 +6363,7 @@
         <v>294</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="147" ht="22.5" customHeight="1">
@@ -6344,7 +6374,7 @@
         <v>296</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="148" ht="22.5" customHeight="1">
@@ -6355,7 +6385,7 @@
         <v>298</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="149" ht="22.5" customHeight="1">
@@ -6366,7 +6396,7 @@
         <v>300</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="150" ht="22.5" customHeight="1">
@@ -6377,7 +6407,7 @@
         <v>302</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="151" ht="22.5" customHeight="1">
@@ -6388,7 +6418,7 @@
         <v>304</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="152" ht="22.5" customHeight="1">
@@ -6399,7 +6429,7 @@
         <v>306</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="153" ht="22.5" customHeight="1">
@@ -6410,7 +6440,7 @@
         <v>308</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="154" ht="22.5" customHeight="1">
@@ -6421,7 +6451,7 @@
         <v>310</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="155" ht="22.5" customHeight="1">
@@ -6432,7 +6462,7 @@
         <v>312</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="156" ht="22.5" customHeight="1">
@@ -6443,7 +6473,7 @@
         <v>314</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="157" ht="22.5" customHeight="1">
@@ -6454,7 +6484,7 @@
         <v>316</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="158" ht="22.5" customHeight="1">
@@ -6465,7 +6495,7 @@
         <v>318</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="159" ht="22.5" customHeight="1">
@@ -6476,7 +6506,7 @@
         <v>320</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="160" ht="22.5" customHeight="1">
@@ -6487,7 +6517,7 @@
         <v>322</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="161" ht="22.5" customHeight="1">
@@ -6498,7 +6528,7 @@
         <v>324</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="162" ht="22.5" customHeight="1">
@@ -6509,7 +6539,7 @@
         <v>326</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="163" ht="22.5" customHeight="1">
@@ -6520,7 +6550,7 @@
         <v>328</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="164" ht="22.5" customHeight="1">
@@ -6531,7 +6561,7 @@
         <v>330</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="165" ht="22.5" customHeight="1">
@@ -6542,7 +6572,7 @@
         <v>332</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="166" ht="22.5" customHeight="1">
@@ -6553,7 +6583,7 @@
         <v>334</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="167" ht="22.5" customHeight="1">
@@ -6564,7 +6594,7 @@
         <v>336</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="168" ht="22.5" customHeight="1">
@@ -6575,7 +6605,7 @@
         <v>338</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="169" ht="22.5" customHeight="1">
@@ -6586,7 +6616,7 @@
         <v>340</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="170" ht="22.5" customHeight="1">
@@ -6597,7 +6627,7 @@
         <v>342</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="171" ht="22.5" customHeight="1">
@@ -6608,7 +6638,7 @@
         <v>344</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="172" ht="22.5" customHeight="1">
@@ -6619,7 +6649,7 @@
         <v>346</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173" ht="22.5" customHeight="1">
@@ -6630,7 +6660,7 @@
         <v>348</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="174" ht="22.5" customHeight="1">
@@ -6641,7 +6671,7 @@
         <v>350</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="175" ht="22.5" customHeight="1">
@@ -6652,7 +6682,7 @@
         <v>352</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="176" ht="22.5" customHeight="1">
@@ -6663,7 +6693,7 @@
         <v>354</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="177" ht="22.5" customHeight="1">
@@ -6674,7 +6704,7 @@
         <v>356</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="178" ht="22.5" customHeight="1">
@@ -6685,7 +6715,7 @@
         <v>358</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179" ht="22.5" customHeight="1">
@@ -6696,7 +6726,7 @@
         <v>360</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="180" ht="22.5" customHeight="1">
@@ -6707,7 +6737,7 @@
         <v>362</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="181" ht="22.5" customHeight="1">
@@ -6718,7 +6748,7 @@
         <v>364</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="182" ht="22.5" customHeight="1">
@@ -6729,7 +6759,7 @@
         <v>366</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="183" ht="22.5" customHeight="1">
@@ -6740,7 +6770,7 @@
         <v>368</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="184" ht="22.5" customHeight="1">
@@ -6751,7 +6781,7 @@
         <v>370</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="185" ht="22.5" customHeight="1">
@@ -6762,7 +6792,7 @@
         <v>372</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="186" ht="22.5" customHeight="1">
@@ -6773,7 +6803,7 @@
         <v>374</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="187" ht="22.5" customHeight="1">
@@ -6784,7 +6814,7 @@
         <v>376</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188" ht="22.5" customHeight="1">
@@ -6795,7 +6825,7 @@
         <v>378</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="189" ht="22.5" customHeight="1">
@@ -6806,7 +6836,7 @@
         <v>380</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="190" ht="22.5" customHeight="1">
@@ -6817,7 +6847,7 @@
         <v>382</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="191" ht="22.5" customHeight="1">
@@ -6828,7 +6858,7 @@
         <v>384</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="192" ht="22.5" customHeight="1">
@@ -6839,7 +6869,7 @@
         <v>386</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="193" ht="22.5" customHeight="1">
@@ -6850,7 +6880,7 @@
         <v>388</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="194" ht="22.5" customHeight="1">
@@ -6861,7 +6891,7 @@
         <v>390</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="195" ht="22.5" customHeight="1">
@@ -6872,7 +6902,7 @@
         <v>392</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="196" ht="22.5" customHeight="1">
@@ -6883,7 +6913,7 @@
         <v>394</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="197" ht="22.5" customHeight="1">
@@ -6894,7 +6924,7 @@
         <v>396</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="198" ht="22.5" customHeight="1">
@@ -6905,7 +6935,7 @@
         <v>398</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="199" ht="22.5" customHeight="1">
@@ -6916,7 +6946,7 @@
         <v>400</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="200" ht="22.5" customHeight="1">
@@ -6927,7 +6957,7 @@
         <v>402</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="201" ht="22.5" customHeight="1">
@@ -6938,7 +6968,7 @@
         <v>404</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="202" ht="22.5" customHeight="1">
@@ -6949,7 +6979,7 @@
         <v>406</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="203" ht="22.5" customHeight="1">
@@ -6960,7 +6990,7 @@
         <v>408</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="204" ht="22.5" customHeight="1">
@@ -6971,7 +7001,7 @@
         <v>410</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="205" ht="22.5" customHeight="1">
@@ -6982,7 +7012,7 @@
         <v>412</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="206" ht="22.5" customHeight="1">
@@ -6993,7 +7023,7 @@
         <v>414</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="207" ht="22.5" customHeight="1">
@@ -7004,7 +7034,7 @@
         <v>416</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="208" ht="22.5" customHeight="1">
@@ -7015,7 +7045,7 @@
         <v>418</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="209" ht="22.5" customHeight="1">
@@ -7026,7 +7056,7 @@
         <v>420</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="210" ht="22.5" customHeight="1">
@@ -7037,7 +7067,7 @@
         <v>422</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="211" ht="22.5" customHeight="1">
@@ -7048,7 +7078,7 @@
         <v>424</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="212" ht="22.5" customHeight="1">
@@ -7059,7 +7089,7 @@
         <v>426</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="213" ht="22.5" customHeight="1">
@@ -7070,7 +7100,7 @@
         <v>428</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="214" ht="22.5" customHeight="1">
@@ -7081,7 +7111,7 @@
         <v>430</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="215" ht="22.5" customHeight="1">
@@ -7092,7 +7122,7 @@
         <v>432</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="216" ht="22.5" customHeight="1">
@@ -7103,7 +7133,7 @@
         <v>434</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="217" ht="22.5" customHeight="1">
@@ -7114,7 +7144,7 @@
         <v>436</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="218" ht="22.5" customHeight="1">
@@ -7125,7 +7155,7 @@
         <v>438</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="219" ht="22.5" customHeight="1">
@@ -7136,7 +7166,7 @@
         <v>440</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="220" ht="22.5" customHeight="1">
@@ -7147,7 +7177,7 @@
         <v>442</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="221" ht="22.5" customHeight="1">
@@ -7158,7 +7188,7 @@
         <v>444</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="222" ht="22.5" customHeight="1">
@@ -7169,7 +7199,7 @@
         <v>446</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="223" ht="22.5" customHeight="1">
@@ -7180,7 +7210,7 @@
         <v>448</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="224" ht="22.5" customHeight="1">
@@ -7191,7 +7221,7 @@
         <v>450</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="225" ht="22.5" customHeight="1">
@@ -7202,7 +7232,7 @@
         <v>452</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="226" ht="22.5" customHeight="1">
@@ -7213,7 +7243,7 @@
         <v>454</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="227" ht="22.5" customHeight="1">
@@ -7224,7 +7254,7 @@
         <v>456</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="228" ht="22.5" customHeight="1">
@@ -7235,7 +7265,7 @@
         <v>458</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="229" ht="22.5" customHeight="1">
@@ -7246,7 +7276,7 @@
         <v>460</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="230" ht="22.5" customHeight="1">
@@ -7257,7 +7287,7 @@
         <v>462</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="231" ht="22.5" customHeight="1">
@@ -7268,7 +7298,7 @@
         <v>464</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="232" ht="22.5" customHeight="1">
@@ -7279,7 +7309,7 @@
         <v>466</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="233" ht="22.5" customHeight="1">
@@ -7290,7 +7320,7 @@
         <v>468</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="234" ht="22.5" customHeight="1">
@@ -7301,7 +7331,7 @@
         <v>470</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="235" ht="22.5" customHeight="1">
@@ -7312,7 +7342,7 @@
         <v>472</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="236" ht="22.5" customHeight="1">
@@ -7323,7 +7353,7 @@
         <v>474</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="237" ht="22.5" customHeight="1">
@@ -7334,7 +7364,7 @@
         <v>476</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="238" ht="22.5" customHeight="1">
@@ -7345,7 +7375,7 @@
         <v>478</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="239" ht="22.5" customHeight="1">
@@ -7356,7 +7386,7 @@
         <v>480</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="240" ht="22.5" customHeight="1">
@@ -7367,7 +7397,7 @@
         <v>482</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="241" ht="22.5" customHeight="1">
@@ -7378,7 +7408,7 @@
         <v>484</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="242" ht="22.5" customHeight="1">
@@ -7389,7 +7419,7 @@
         <v>486</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="243" ht="22.5" customHeight="1">
@@ -7400,7 +7430,7 @@
         <v>488</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="244" ht="22.5" customHeight="1">
@@ -7411,7 +7441,7 @@
         <v>490</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="245" ht="22.5" customHeight="1">
@@ -7422,7 +7452,7 @@
         <v>492</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="246" ht="22.5" customHeight="1">
@@ -7433,7 +7463,7 @@
         <v>494</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="247" ht="22.5" customHeight="1">
@@ -7444,7 +7474,7 @@
         <v>496</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="248" ht="22.5" customHeight="1">
@@ -7455,7 +7485,7 @@
         <v>498</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="249" ht="22.5" customHeight="1">
@@ -7466,7 +7496,7 @@
         <v>500</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="250" ht="22.5" customHeight="1">
@@ -7477,7 +7507,7 @@
         <v>502</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="251" ht="22.5" customHeight="1">
@@ -7488,7 +7518,7 @@
         <v>504</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="252" ht="22.5" customHeight="1">
@@ -7499,7 +7529,7 @@
         <v>506</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="253" ht="22.5" customHeight="1">
@@ -7510,7 +7540,7 @@
         <v>508</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="254" ht="22.5" customHeight="1">
@@ -7521,7 +7551,7 @@
         <v>510</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="255" ht="22.5" customHeight="1">
@@ -7532,7 +7562,7 @@
         <v>512</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="256" ht="22.5" customHeight="1">
@@ -7543,7 +7573,7 @@
         <v>514</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="257" ht="22.5" customHeight="1">
@@ -7554,7 +7584,7 @@
         <v>516</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="258" ht="22.5" customHeight="1">
@@ -7565,7 +7595,7 @@
         <v>518</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="259" ht="22.5" customHeight="1">
@@ -7576,7 +7606,7 @@
         <v>520</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="260" ht="22.5" customHeight="1">
@@ -7587,7 +7617,7 @@
         <v>522</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="261" ht="22.5" customHeight="1">
@@ -7598,7 +7628,7 @@
         <v>454</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="262" ht="22.5" customHeight="1">
@@ -7609,7 +7639,7 @@
         <v>525</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="263" ht="22.5" customHeight="1">
@@ -7620,7 +7650,7 @@
         <v>527</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="264" ht="22.5" customHeight="1">
@@ -7631,7 +7661,7 @@
         <v>529</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="265" ht="22.5" customHeight="1">
@@ -7642,7 +7672,7 @@
         <v>450</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="266" ht="22.5" customHeight="1">
@@ -7653,7 +7683,7 @@
         <v>532</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="267" ht="22.5" customHeight="1">
@@ -7664,7 +7694,7 @@
         <v>534</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="268" ht="22.5" customHeight="1">
@@ -7675,7 +7705,7 @@
         <v>536</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="269" ht="22.5" customHeight="1">
@@ -7686,7 +7716,7 @@
         <v>538</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="270" ht="22.5" customHeight="1">
@@ -7697,7 +7727,7 @@
         <v>540</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="271" ht="22.5" customHeight="1">
@@ -7708,7 +7738,7 @@
         <v>542</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="272" ht="22.5" customHeight="1">
@@ -7719,7 +7749,7 @@
         <v>544</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="273" ht="22.5" customHeight="1">
@@ -7730,7 +7760,7 @@
         <v>546</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="274" ht="22.5" customHeight="1">
@@ -7741,7 +7771,7 @@
         <v>548</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="275" ht="22.5" customHeight="1">
@@ -7752,7 +7782,7 @@
         <v>550</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="276" ht="22.5" customHeight="1">
@@ -7763,7 +7793,7 @@
         <v>552</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="277" ht="22.5" customHeight="1">
@@ -7774,7 +7804,7 @@
         <v>554</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="278" ht="22.5" customHeight="1">
@@ -7785,7 +7815,7 @@
         <v>556</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="279" ht="22.5" customHeight="1">
@@ -7796,7 +7826,7 @@
         <v>558</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="280" ht="22.5" customHeight="1">
@@ -7807,7 +7837,7 @@
         <v>560</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="281" ht="22.5" customHeight="1">
@@ -7818,7 +7848,7 @@
         <v>562</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="282" ht="22.5" customHeight="1">
@@ -7829,7 +7859,7 @@
         <v>564</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="283" ht="22.5" customHeight="1">
@@ -7840,7 +7870,7 @@
         <v>566</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="284" ht="22.5" customHeight="1">
@@ -7851,7 +7881,7 @@
         <v>568</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="285" ht="22.5" customHeight="1">
@@ -7862,7 +7892,7 @@
         <v>570</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="286" ht="22.5" customHeight="1">
@@ -7873,7 +7903,7 @@
         <v>572</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="287" ht="22.5" customHeight="1">
@@ -7884,7 +7914,7 @@
         <v>574</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="288" ht="22.5" customHeight="1">
@@ -7895,7 +7925,7 @@
         <v>576</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="289" ht="22.5" customHeight="1">
@@ -7906,7 +7936,7 @@
         <v>578</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="290" ht="22.5" customHeight="1">
@@ -7917,7 +7947,7 @@
         <v>580</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="291" ht="22.5" customHeight="1">
@@ -7928,7 +7958,7 @@
         <v>582</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="292" ht="22.5" customHeight="1">
@@ -7939,7 +7969,7 @@
         <v>584</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="293" ht="22.5" customHeight="1">
@@ -7950,7 +7980,7 @@
         <v>586</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="294" ht="22.5" customHeight="1">
@@ -7961,7 +7991,7 @@
         <v>588</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="295" ht="22.5" customHeight="1">
@@ -7972,7 +8002,7 @@
         <v>590</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="296" ht="22.5" customHeight="1">
@@ -7983,7 +8013,7 @@
         <v>592</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="297" ht="22.5" customHeight="1">
@@ -7994,7 +8024,7 @@
         <v>594</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="298" ht="22.5" customHeight="1">
@@ -8005,7 +8035,7 @@
         <v>596</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="299" ht="22.5" customHeight="1">
@@ -8016,7 +8046,7 @@
         <v>598</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="300" ht="22.5" customHeight="1">
@@ -8027,7 +8057,7 @@
         <v>600</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="301" ht="22.5" customHeight="1">
@@ -8038,7 +8068,7 @@
         <v>602</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="302" ht="22.5" customHeight="1">
@@ -8049,7 +8079,7 @@
         <v>604</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="303" ht="22.5" customHeight="1">
@@ -8060,7 +8090,7 @@
         <v>606</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="304" ht="22.5" customHeight="1">
@@ -8071,7 +8101,7 @@
         <v>608</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="305" ht="22.5" customHeight="1">
@@ -8082,7 +8112,7 @@
         <v>610</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="306" ht="22.5" customHeight="1">
@@ -8093,7 +8123,7 @@
         <v>612</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="307" ht="22.5" customHeight="1">
@@ -8104,7 +8134,7 @@
         <v>614</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="308" ht="22.5" customHeight="1">
@@ -8115,7 +8145,7 @@
         <v>616</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="309" ht="22.5" customHeight="1">
@@ -8126,7 +8156,7 @@
         <v>618</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="310" ht="22.5" customHeight="1">
@@ -8137,7 +8167,7 @@
         <v>620</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="311" ht="22.5" customHeight="1">
@@ -8148,7 +8178,7 @@
         <v>622</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="312" ht="22.5" customHeight="1">
@@ -8159,7 +8189,7 @@
         <v>624</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="313" ht="22.5" customHeight="1">
@@ -8170,7 +8200,7 @@
         <v>626</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="314" ht="22.5" customHeight="1">
@@ -8181,7 +8211,7 @@
         <v>628</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="315" ht="22.5" customHeight="1">
@@ -8192,7 +8222,7 @@
         <v>630</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="316" ht="22.5" customHeight="1">
@@ -8203,7 +8233,7 @@
         <v>632</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="317" ht="22.5" customHeight="1">
@@ -8214,7 +8244,7 @@
         <v>634</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="318" ht="22.5" customHeight="1">
@@ -8225,7 +8255,7 @@
         <v>636</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="319" ht="22.5" customHeight="1">
@@ -8236,7 +8266,7 @@
         <v>638</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="320" ht="22.5" customHeight="1">
@@ -8247,7 +8277,7 @@
         <v>640</v>
       </c>
       <c r="C320" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="321" ht="22.5" customHeight="1">
@@ -8258,7 +8288,7 @@
         <v>642</v>
       </c>
       <c r="C321" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="322" ht="22.5" customHeight="1">
@@ -8269,7 +8299,7 @@
         <v>644</v>
       </c>
       <c r="C322" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="323" ht="22.5" customHeight="1">
@@ -8280,7 +8310,7 @@
         <v>646</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="324" ht="22.5" customHeight="1">
@@ -8291,7 +8321,7 @@
         <v>648</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="325" ht="22.5" customHeight="1">
@@ -8302,7 +8332,7 @@
         <v>650</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="326" ht="22.5" customHeight="1">
@@ -8313,7 +8343,7 @@
         <v>652</v>
       </c>
       <c r="C326" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="327" ht="22.5" customHeight="1">
@@ -8324,7 +8354,7 @@
         <v>654</v>
       </c>
       <c r="C327" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="328" ht="22.5" customHeight="1">
@@ -8335,7 +8365,7 @@
         <v>656</v>
       </c>
       <c r="C328" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="329" ht="22.5" customHeight="1">
@@ -8346,7 +8376,7 @@
         <v>658</v>
       </c>
       <c r="C329" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="330" ht="22.5" customHeight="1">
@@ -8357,7 +8387,7 @@
         <v>660</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="331" ht="22.5" customHeight="1">
@@ -8368,7 +8398,7 @@
         <v>662</v>
       </c>
       <c r="C331" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="332" ht="22.5" customHeight="1">
@@ -8379,7 +8409,7 @@
         <v>664</v>
       </c>
       <c r="C332" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="333" ht="22.5" customHeight="1">
@@ -8390,7 +8420,7 @@
         <v>666</v>
       </c>
       <c r="C333" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="334" ht="22.5" customHeight="1">
@@ -8401,7 +8431,7 @@
         <v>668</v>
       </c>
       <c r="C334" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="335" ht="22.5" customHeight="1">
@@ -8412,7 +8442,7 @@
         <v>670</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="336" ht="22.5" customHeight="1">
@@ -8423,7 +8453,7 @@
         <v>672</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="337" ht="22.5" customHeight="1">
@@ -8434,7 +8464,7 @@
         <v>674</v>
       </c>
       <c r="C337" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="338" ht="22.5" customHeight="1">
@@ -8445,7 +8475,7 @@
         <v>676</v>
       </c>
       <c r="C338" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="339" ht="22.5" customHeight="1">
@@ -8456,7 +8486,7 @@
         <v>678</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="340" ht="22.5" customHeight="1">
@@ -8467,7 +8497,7 @@
         <v>680</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="341" ht="22.5" customHeight="1">
@@ -8478,7 +8508,7 @@
         <v>682</v>
       </c>
       <c r="C341" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="342" ht="22.5" customHeight="1">
@@ -8489,7 +8519,7 @@
         <v>684</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="343" ht="22.5" customHeight="1">
@@ -8500,7 +8530,7 @@
         <v>686</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="344" ht="22.5" customHeight="1">
@@ -8511,7 +8541,7 @@
         <v>688</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="345" ht="22.5" customHeight="1">
@@ -8522,7 +8552,7 @@
         <v>690</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="346" ht="22.5" customHeight="1">
@@ -8533,7 +8563,7 @@
         <v>692</v>
       </c>
       <c r="C346" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="347" ht="22.5" customHeight="1">
@@ -8544,7 +8574,7 @@
         <v>694</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="348" ht="22.5" customHeight="1">
@@ -8555,7 +8585,7 @@
         <v>696</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="349" ht="22.5" customHeight="1">
@@ -8566,7 +8596,7 @@
         <v>698</v>
       </c>
       <c r="C349" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="350" ht="22.5" customHeight="1">
@@ -8577,7 +8607,7 @@
         <v>700</v>
       </c>
       <c r="C350" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="351" ht="22.5" customHeight="1">
@@ -8588,7 +8618,7 @@
         <v>702</v>
       </c>
       <c r="C351" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="352" ht="22.5" customHeight="1">
@@ -8599,7 +8629,7 @@
         <v>704</v>
       </c>
       <c r="C352" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="353" ht="22.5" customHeight="1">
@@ -8610,7 +8640,7 @@
         <v>706</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="354" ht="22.5" customHeight="1">
@@ -8621,7 +8651,7 @@
         <v>708</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="355" ht="22.5" customHeight="1">
@@ -8632,7 +8662,7 @@
         <v>710</v>
       </c>
       <c r="C355" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="356" ht="22.5" customHeight="1">
@@ -8643,7 +8673,7 @@
         <v>712</v>
       </c>
       <c r="C356" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="357" ht="22.5" customHeight="1">
@@ -8654,7 +8684,7 @@
         <v>714</v>
       </c>
       <c r="C357" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="358" ht="22.5" customHeight="1">
@@ -8665,7 +8695,7 @@
         <v>716</v>
       </c>
       <c r="C358" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="359" ht="22.5" customHeight="1">
@@ -8676,7 +8706,7 @@
         <v>718</v>
       </c>
       <c r="C359" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="360" ht="22.5" customHeight="1">
@@ -8687,7 +8717,7 @@
         <v>720</v>
       </c>
       <c r="C360" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="361" ht="22.5" customHeight="1">
@@ -8698,7 +8728,7 @@
         <v>722</v>
       </c>
       <c r="C361" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="362" ht="22.5" customHeight="1">
@@ -8709,7 +8739,7 @@
         <v>724</v>
       </c>
       <c r="C362" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="363" ht="22.5" customHeight="1">
@@ -8720,7 +8750,7 @@
         <v>726</v>
       </c>
       <c r="C363" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="364" ht="22.5" customHeight="1">
@@ -8731,7 +8761,7 @@
         <v>728</v>
       </c>
       <c r="C364" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="365" ht="22.5" customHeight="1">
@@ -8742,7 +8772,7 @@
         <v>730</v>
       </c>
       <c r="C365" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="366" ht="22.5" customHeight="1">
@@ -8753,7 +8783,7 @@
         <v>732</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="367" ht="22.5" customHeight="1">
@@ -8764,7 +8794,7 @@
         <v>734</v>
       </c>
       <c r="C367" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="368" ht="22.5" customHeight="1">
@@ -8775,7 +8805,7 @@
         <v>736</v>
       </c>
       <c r="C368" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="369" ht="22.5" customHeight="1">
@@ -8786,7 +8816,7 @@
         <v>738</v>
       </c>
       <c r="C369" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="370" ht="22.5" customHeight="1">
@@ -8797,7 +8827,7 @@
         <v>740</v>
       </c>
       <c r="C370" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="371" ht="22.5" customHeight="1">
@@ -8808,7 +8838,7 @@
         <v>742</v>
       </c>
       <c r="C371" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="372" ht="22.5" customHeight="1">
@@ -8819,7 +8849,7 @@
         <v>744</v>
       </c>
       <c r="C372" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="373" ht="22.5" customHeight="1">
@@ -8830,7 +8860,7 @@
         <v>746</v>
       </c>
       <c r="C373" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="374" ht="22.5" customHeight="1">
@@ -8841,7 +8871,7 @@
         <v>748</v>
       </c>
       <c r="C374" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="375" ht="22.5" customHeight="1">
@@ -8852,7 +8882,7 @@
         <v>750</v>
       </c>
       <c r="C375" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="376" ht="22.5" customHeight="1">
@@ -8863,7 +8893,7 @@
         <v>752</v>
       </c>
       <c r="C376" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="377" ht="22.5" customHeight="1">
@@ -8874,7 +8904,7 @@
         <v>754</v>
       </c>
       <c r="C377" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="378" ht="22.5" customHeight="1">
@@ -8885,7 +8915,7 @@
         <v>756</v>
       </c>
       <c r="C378" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="379" ht="22.5" customHeight="1">
@@ -8896,7 +8926,7 @@
         <v>758</v>
       </c>
       <c r="C379" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="380" ht="22.5" customHeight="1">
@@ -8907,7 +8937,7 @@
         <v>760</v>
       </c>
       <c r="C380" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="381" ht="22.5" customHeight="1">
@@ -8918,7 +8948,7 @@
         <v>762</v>
       </c>
       <c r="C381" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="382" ht="22.5" customHeight="1">
@@ -8929,7 +8959,7 @@
         <v>764</v>
       </c>
       <c r="C382" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="383" ht="22.5" customHeight="1">
@@ -8940,7 +8970,7 @@
         <v>766</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="384" ht="22.5" customHeight="1">
@@ -8951,7 +8981,7 @@
         <v>768</v>
       </c>
       <c r="C384" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="385" ht="22.5" customHeight="1">
@@ -8962,7 +8992,7 @@
         <v>770</v>
       </c>
       <c r="C385" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="386" ht="22.5" customHeight="1">
@@ -8973,7 +9003,7 @@
         <v>772</v>
       </c>
       <c r="C386" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="387" ht="22.5" customHeight="1">
@@ -8984,7 +9014,7 @@
         <v>774</v>
       </c>
       <c r="C387" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="388" ht="22.5" customHeight="1">
@@ -8995,7 +9025,7 @@
         <v>776</v>
       </c>
       <c r="C388" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="389" ht="22.5" customHeight="1">
@@ -9006,7 +9036,7 @@
         <v>778</v>
       </c>
       <c r="C389" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="390" ht="22.5" customHeight="1">
@@ -9017,7 +9047,7 @@
         <v>780</v>
       </c>
       <c r="C390" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="391" ht="22.5" customHeight="1">
@@ -9028,7 +9058,7 @@
         <v>782</v>
       </c>
       <c r="C391" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="392" ht="22.5" customHeight="1">
@@ -9039,7 +9069,7 @@
         <v>784</v>
       </c>
       <c r="C392" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="393" ht="22.5" customHeight="1">
@@ -9050,7 +9080,7 @@
         <v>786</v>
       </c>
       <c r="C393" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="394" ht="22.5" customHeight="1">
@@ -9061,7 +9091,7 @@
         <v>788</v>
       </c>
       <c r="C394" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="395" ht="22.5" customHeight="1">
@@ -9072,7 +9102,7 @@
         <v>790</v>
       </c>
       <c r="C395" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="396" ht="22.5" customHeight="1">
@@ -9083,7 +9113,7 @@
         <v>792</v>
       </c>
       <c r="C396" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="397" ht="22.5" customHeight="1">
@@ -9094,7 +9124,7 @@
         <v>794</v>
       </c>
       <c r="C397" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="398" ht="22.5" customHeight="1">
@@ -9105,7 +9135,7 @@
         <v>796</v>
       </c>
       <c r="C398" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="399" ht="22.5" customHeight="1">
@@ -9116,7 +9146,7 @@
         <v>798</v>
       </c>
       <c r="C399" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="400" ht="22.5" customHeight="1">
@@ -9127,7 +9157,7 @@
         <v>800</v>
       </c>
       <c r="C400" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="401" ht="22.5" customHeight="1">
@@ -9138,7 +9168,7 @@
         <v>802</v>
       </c>
       <c r="C401" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="402" ht="22.5" customHeight="1">
@@ -9149,7 +9179,7 @@
         <v>804</v>
       </c>
       <c r="C402" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="403" ht="22.5" customHeight="1">
@@ -9160,7 +9190,7 @@
         <v>806</v>
       </c>
       <c r="C403" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="404" ht="22.5" customHeight="1">
@@ -9171,7 +9201,7 @@
         <v>808</v>
       </c>
       <c r="C404" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="405" ht="22.5" customHeight="1">
@@ -9182,7 +9212,7 @@
         <v>810</v>
       </c>
       <c r="C405" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="406" ht="22.5" customHeight="1">
@@ -9193,7 +9223,7 @@
         <v>812</v>
       </c>
       <c r="C406" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="407" ht="22.5" customHeight="1">
@@ -9204,7 +9234,7 @@
         <v>814</v>
       </c>
       <c r="C407" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="408" ht="22.5" customHeight="1">
@@ -9215,7 +9245,7 @@
         <v>816</v>
       </c>
       <c r="C408" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="409" ht="22.5" customHeight="1">
@@ -9226,7 +9256,7 @@
         <v>818</v>
       </c>
       <c r="C409" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="410" ht="22.5" customHeight="1">
@@ -9237,7 +9267,7 @@
         <v>820</v>
       </c>
       <c r="C410" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="411" ht="22.5" customHeight="1">
@@ -9248,7 +9278,7 @@
         <v>822</v>
       </c>
       <c r="C411" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="412" ht="22.5" customHeight="1">
@@ -9259,7 +9289,7 @@
         <v>824</v>
       </c>
       <c r="C412" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="413" ht="22.5" customHeight="1">
@@ -9270,7 +9300,7 @@
         <v>826</v>
       </c>
       <c r="C413" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="414" ht="22.5" customHeight="1">
@@ -9281,7 +9311,7 @@
         <v>828</v>
       </c>
       <c r="C414" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="415" ht="22.5" customHeight="1">
@@ -9292,7 +9322,7 @@
         <v>830</v>
       </c>
       <c r="C415" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="416" ht="22.5" customHeight="1">
@@ -9303,7 +9333,7 @@
         <v>832</v>
       </c>
       <c r="C416" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="417" ht="22.5" customHeight="1">
@@ -9314,7 +9344,7 @@
         <v>834</v>
       </c>
       <c r="C417" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="418" ht="22.5" customHeight="1">
@@ -9325,7 +9355,7 @@
         <v>836</v>
       </c>
       <c r="C418" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="419" ht="22.5" customHeight="1">
@@ -9336,7 +9366,7 @@
         <v>838</v>
       </c>
       <c r="C419" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="420" ht="22.5" customHeight="1">
@@ -9347,7 +9377,7 @@
         <v>840</v>
       </c>
       <c r="C420" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="421" ht="22.5" customHeight="1">
@@ -9358,7 +9388,7 @@
         <v>842</v>
       </c>
       <c r="C421" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="422" ht="22.5" customHeight="1">
@@ -9369,7 +9399,7 @@
         <v>844</v>
       </c>
       <c r="C422" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="423" ht="22.5" customHeight="1">
@@ -9380,7 +9410,7 @@
         <v>846</v>
       </c>
       <c r="C423" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="424" ht="22.5" customHeight="1">
@@ -9391,7 +9421,7 @@
         <v>848</v>
       </c>
       <c r="C424" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="425" ht="22.5" customHeight="1">
@@ -9402,7 +9432,7 @@
         <v>96</v>
       </c>
       <c r="C425" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="426" ht="22.5" customHeight="1">
@@ -9413,7 +9443,7 @@
         <v>851</v>
       </c>
       <c r="C426" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="427" ht="22.5" customHeight="1">
@@ -9424,7 +9454,7 @@
         <v>853</v>
       </c>
       <c r="C427" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="428" ht="22.5" customHeight="1">
@@ -9435,7 +9465,7 @@
         <v>855</v>
       </c>
       <c r="C428" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="429" ht="22.5" customHeight="1">
@@ -9446,7 +9476,7 @@
         <v>857</v>
       </c>
       <c r="C429" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="430" ht="22.5" customHeight="1">
@@ -9457,7 +9487,7 @@
         <v>859</v>
       </c>
       <c r="C430" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="431" ht="22.5" customHeight="1">
@@ -9468,7 +9498,7 @@
         <v>861</v>
       </c>
       <c r="C431" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="432" ht="22.5" customHeight="1">
@@ -9479,7 +9509,7 @@
         <v>863</v>
       </c>
       <c r="C432" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="433" ht="22.5" customHeight="1">
@@ -9490,7 +9520,7 @@
         <v>865</v>
       </c>
       <c r="C433" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="434" ht="22.5" customHeight="1">
@@ -9501,7 +9531,7 @@
         <v>867</v>
       </c>
       <c r="C434" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="435" ht="22.5" customHeight="1">
@@ -9512,7 +9542,7 @@
         <v>869</v>
       </c>
       <c r="C435" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="436" ht="22.5" customHeight="1">
@@ -9523,7 +9553,7 @@
         <v>871</v>
       </c>
       <c r="C436" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="437" ht="22.5" customHeight="1">
@@ -9534,7 +9564,7 @@
         <v>873</v>
       </c>
       <c r="C437" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="438" ht="22.5" customHeight="1">
@@ -9545,7 +9575,7 @@
         <v>875</v>
       </c>
       <c r="C438" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="439" ht="22.5" customHeight="1">
@@ -9556,7 +9586,7 @@
         <v>877</v>
       </c>
       <c r="C439" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="440" ht="22.5" customHeight="1">
@@ -9567,7 +9597,7 @@
         <v>879</v>
       </c>
       <c r="C440" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="441" ht="22.5" customHeight="1">
@@ -9578,7 +9608,7 @@
         <v>881</v>
       </c>
       <c r="C441" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="442" ht="22.5" customHeight="1">
@@ -9589,7 +9619,7 @@
         <v>883</v>
       </c>
       <c r="C442" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="443" ht="22.5" customHeight="1">
@@ -9600,7 +9630,7 @@
         <v>885</v>
       </c>
       <c r="C443" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="444" ht="22.5" customHeight="1">
@@ -9611,7 +9641,7 @@
         <v>887</v>
       </c>
       <c r="C444" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="445" ht="22.5" customHeight="1">
@@ -9622,7 +9652,7 @@
         <v>889</v>
       </c>
       <c r="C445" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="446" ht="22.5" customHeight="1">
@@ -9633,7 +9663,7 @@
         <v>891</v>
       </c>
       <c r="C446" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="447" ht="22.5" customHeight="1">
@@ -9644,7 +9674,7 @@
         <v>893</v>
       </c>
       <c r="C447" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="448" ht="22.5" customHeight="1">
@@ -9655,7 +9685,7 @@
         <v>895</v>
       </c>
       <c r="C448" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="449" ht="22.5" customHeight="1">
@@ -9666,7 +9696,7 @@
         <v>897</v>
       </c>
       <c r="C449" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="450" ht="22.5" customHeight="1">
@@ -9677,7 +9707,7 @@
         <v>899</v>
       </c>
       <c r="C450" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="451" ht="22.5" customHeight="1">
@@ -9688,7 +9718,7 @@
         <v>901</v>
       </c>
       <c r="C451" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="452" ht="22.5" customHeight="1">
@@ -9699,7 +9729,7 @@
         <v>903</v>
       </c>
       <c r="C452" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="453" ht="22.5" customHeight="1">
@@ -9710,7 +9740,7 @@
         <v>905</v>
       </c>
       <c r="C453" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="454" ht="22.5" customHeight="1">
@@ -9721,7 +9751,7 @@
         <v>907</v>
       </c>
       <c r="C454" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="455" ht="22.5" customHeight="1">
@@ -9732,7 +9762,7 @@
         <v>909</v>
       </c>
       <c r="C455" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="456" ht="22.5" customHeight="1">
@@ -9743,7 +9773,7 @@
         <v>911</v>
       </c>
       <c r="C456" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="457" ht="22.5" customHeight="1">
@@ -9754,7 +9784,7 @@
         <v>913</v>
       </c>
       <c r="C457" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="458" ht="22.5" customHeight="1">
@@ -9765,7 +9795,7 @@
         <v>915</v>
       </c>
       <c r="C458" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="459" ht="22.5" customHeight="1">
@@ -9776,7 +9806,7 @@
         <v>917</v>
       </c>
       <c r="C459" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="460" ht="22.5" customHeight="1">
@@ -9787,7 +9817,7 @@
         <v>919</v>
       </c>
       <c r="C460" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="461" ht="22.5" customHeight="1">
@@ -9798,7 +9828,7 @@
         <v>921</v>
       </c>
       <c r="C461" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="462" ht="22.5" customHeight="1">
@@ -9809,7 +9839,7 @@
         <v>923</v>
       </c>
       <c r="C462" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="463" ht="22.5" customHeight="1">
@@ -9820,7 +9850,7 @@
         <v>925</v>
       </c>
       <c r="C463" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="464" ht="22.5" customHeight="1">
@@ -9831,7 +9861,7 @@
         <v>927</v>
       </c>
       <c r="C464" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="465" ht="22.5" customHeight="1">
@@ -9842,7 +9872,7 @@
         <v>929</v>
       </c>
       <c r="C465" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="466" ht="22.5" customHeight="1">
@@ -9853,7 +9883,7 @@
         <v>931</v>
       </c>
       <c r="C466" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="467" ht="22.5" customHeight="1">
@@ -9864,7 +9894,7 @@
         <v>933</v>
       </c>
       <c r="C467" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="468" ht="22.5" customHeight="1">
@@ -9875,7 +9905,7 @@
         <v>935</v>
       </c>
       <c r="C468" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="469" ht="22.5" customHeight="1">
@@ -9886,7 +9916,7 @@
         <v>937</v>
       </c>
       <c r="C469" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="470" ht="22.5" customHeight="1">
@@ -9897,7 +9927,7 @@
         <v>939</v>
       </c>
       <c r="C470" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="471" ht="22.5" customHeight="1">
@@ -9908,7 +9938,7 @@
         <v>941</v>
       </c>
       <c r="C471" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="472" ht="22.5" customHeight="1">
@@ -9919,7 +9949,7 @@
         <v>943</v>
       </c>
       <c r="C472" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="473" ht="22.5" customHeight="1">
@@ -9930,7 +9960,7 @@
         <v>945</v>
       </c>
       <c r="C473" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="474" ht="22.5" customHeight="1">
@@ -9941,7 +9971,7 @@
         <v>947</v>
       </c>
       <c r="C474" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="475" ht="22.5" customHeight="1">
@@ -9952,7 +9982,7 @@
         <v>949</v>
       </c>
       <c r="C475" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="476" ht="22.5" customHeight="1">
@@ -9963,7 +9993,7 @@
         <v>951</v>
       </c>
       <c r="C476" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="477" ht="22.5" customHeight="1">
@@ -9974,7 +10004,7 @@
         <v>953</v>
       </c>
       <c r="C477" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="478" ht="22.5" customHeight="1">
@@ -9985,7 +10015,7 @@
         <v>955</v>
       </c>
       <c r="C478" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="479" ht="22.5" customHeight="1">
@@ -9996,7 +10026,7 @@
         <v>957</v>
       </c>
       <c r="C479" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="480" ht="22.5" customHeight="1">
@@ -10007,7 +10037,7 @@
         <v>959</v>
       </c>
       <c r="C480" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="481" ht="22.5" customHeight="1">
@@ -10018,7 +10048,7 @@
         <v>961</v>
       </c>
       <c r="C481" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="482" ht="22.5" customHeight="1">
@@ -10029,7 +10059,7 @@
         <v>963</v>
       </c>
       <c r="C482" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="483" ht="22.5" customHeight="1">
@@ -10040,7 +10070,7 @@
         <v>965</v>
       </c>
       <c r="C483" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="484" ht="22.5" customHeight="1">
@@ -10051,7 +10081,7 @@
         <v>967</v>
       </c>
       <c r="C484" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="485" ht="22.5" customHeight="1">
@@ -10062,7 +10092,7 @@
         <v>969</v>
       </c>
       <c r="C485" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="486" ht="22.5" customHeight="1">
@@ -10073,7 +10103,7 @@
         <v>971</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="487" ht="22.5" customHeight="1">
@@ -10084,7 +10114,7 @@
         <v>973</v>
       </c>
       <c r="C487" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="488" ht="22.5" customHeight="1">
@@ -10095,7 +10125,7 @@
         <v>975</v>
       </c>
       <c r="C488" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="489" ht="22.5" customHeight="1">
@@ -10106,7 +10136,7 @@
         <v>977</v>
       </c>
       <c r="C489" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="490" ht="22.5" customHeight="1">
@@ -10117,7 +10147,7 @@
         <v>979</v>
       </c>
       <c r="C490" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="491" ht="22.5" customHeight="1">
@@ -10128,7 +10158,7 @@
         <v>981</v>
       </c>
       <c r="C491" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="492" ht="22.5" customHeight="1">
@@ -10139,7 +10169,7 @@
         <v>983</v>
       </c>
       <c r="C492" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="493" ht="22.5" customHeight="1">
@@ -10150,7 +10180,7 @@
         <v>985</v>
       </c>
       <c r="C493" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="494" ht="22.5" customHeight="1">
@@ -10161,7 +10191,7 @@
         <v>987</v>
       </c>
       <c r="C494" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="495" ht="22.5" customHeight="1">
@@ -10172,7 +10202,7 @@
         <v>989</v>
       </c>
       <c r="C495" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="496" ht="22.5" customHeight="1">
@@ -10183,7 +10213,7 @@
         <v>991</v>
       </c>
       <c r="C496" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="497" ht="22.5" customHeight="1">
@@ -10194,7 +10224,7 @@
         <v>993</v>
       </c>
       <c r="C497" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="498" ht="22.5" customHeight="1">
@@ -10205,7 +10235,7 @@
         <v>995</v>
       </c>
       <c r="C498" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="499" ht="22.5" customHeight="1">
@@ -10216,7 +10246,7 @@
         <v>997</v>
       </c>
       <c r="C499" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="500" ht="22.5" customHeight="1">
@@ -10227,7 +10257,7 @@
         <v>999</v>
       </c>
       <c r="C500" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="501" ht="22.5" customHeight="1">
@@ -10238,7 +10268,7 @@
         <v>1001</v>
       </c>
       <c r="C501" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="502" ht="22.5" customHeight="1">
@@ -10249,7 +10279,7 @@
         <v>1003</v>
       </c>
       <c r="C502" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="503" ht="22.5" customHeight="1">
@@ -10260,7 +10290,7 @@
         <v>1005</v>
       </c>
       <c r="C503" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="504" ht="22.5" customHeight="1">
@@ -10271,7 +10301,7 @@
         <v>1007</v>
       </c>
       <c r="C504" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="505" ht="22.5" customHeight="1">
@@ -10282,7 +10312,7 @@
         <v>1009</v>
       </c>
       <c r="C505" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="506" ht="22.5" customHeight="1">
@@ -10293,7 +10323,7 @@
         <v>1011</v>
       </c>
       <c r="C506" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="507" ht="22.5" customHeight="1">
@@ -10304,7 +10334,7 @@
         <v>1013</v>
       </c>
       <c r="C507" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="508" ht="22.5" customHeight="1">
@@ -10315,7 +10345,7 @@
         <v>1015</v>
       </c>
       <c r="C508" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="509" ht="22.5" customHeight="1">
@@ -10326,7 +10356,7 @@
         <v>1017</v>
       </c>
       <c r="C509" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="510" ht="22.5" customHeight="1">
@@ -10337,7 +10367,7 @@
         <v>1019</v>
       </c>
       <c r="C510" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="511" ht="22.5" customHeight="1">
@@ -10348,7 +10378,7 @@
         <v>1021</v>
       </c>
       <c r="C511" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="512" ht="22.5" customHeight="1">
@@ -10359,7 +10389,7 @@
         <v>1023</v>
       </c>
       <c r="C512" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="513" ht="22.5" customHeight="1">
@@ -10370,7 +10400,7 @@
         <v>1025</v>
       </c>
       <c r="C513" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="514" ht="22.5" customHeight="1">
@@ -10381,7 +10411,7 @@
         <v>1027</v>
       </c>
       <c r="C514" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="515" ht="22.5" customHeight="1">
@@ -10392,7 +10422,7 @@
         <v>1029</v>
       </c>
       <c r="C515" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="516" ht="22.5" customHeight="1">
@@ -10403,7 +10433,7 @@
         <v>1031</v>
       </c>
       <c r="C516" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="517" ht="22.5" customHeight="1">
@@ -10414,7 +10444,7 @@
         <v>1033</v>
       </c>
       <c r="C517" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="518" ht="22.5" customHeight="1">
@@ -10425,7 +10455,7 @@
         <v>1035</v>
       </c>
       <c r="C518" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="519" ht="22.5" customHeight="1">
@@ -10436,7 +10466,7 @@
         <v>1037</v>
       </c>
       <c r="C519" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="520" ht="22.5" customHeight="1">
@@ -10447,7 +10477,7 @@
         <v>1039</v>
       </c>
       <c r="C520" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="521" ht="22.5" customHeight="1">
@@ -10458,7 +10488,7 @@
         <v>1041</v>
       </c>
       <c r="C521" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="522" ht="22.5" customHeight="1">
@@ -10469,18 +10499,18 @@
         <v>1043</v>
       </c>
       <c r="C522" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="523" ht="22.5" customHeight="1">
       <c r="A523" s="4" t="s">
         <v>1044</v>
       </c>
-      <c r="B523" s="8" t="s">
+      <c r="B523" s="10" t="s">
         <v>1045</v>
       </c>
       <c r="C523" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="524" ht="22.5" customHeight="1">
@@ -10491,7 +10521,7 @@
         <v>1047</v>
       </c>
       <c r="C524" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="525" ht="22.5" customHeight="1">
@@ -10502,7 +10532,7 @@
         <v>1049</v>
       </c>
       <c r="C525" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="526" ht="22.5" customHeight="1">
@@ -10513,7 +10543,7 @@
         <v>1051</v>
       </c>
       <c r="C526" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="527" ht="22.5" customHeight="1">
@@ -10524,7 +10554,7 @@
         <v>1053</v>
       </c>
       <c r="C527" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="528" ht="22.5" customHeight="1">
@@ -10535,7 +10565,7 @@
         <v>1055</v>
       </c>
       <c r="C528" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="529" ht="22.5" customHeight="1">
@@ -10546,7 +10576,7 @@
         <v>1057</v>
       </c>
       <c r="C529" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="530" ht="22.5" customHeight="1">
@@ -10557,7 +10587,7 @@
         <v>1059</v>
       </c>
       <c r="C530" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="531" ht="22.5" customHeight="1">
@@ -10568,7 +10598,7 @@
         <v>1061</v>
       </c>
       <c r="C531" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="532" ht="22.5" customHeight="1">
@@ -10579,7 +10609,7 @@
         <v>1063</v>
       </c>
       <c r="C532" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="533" ht="22.5" customHeight="1">
@@ -10590,7 +10620,7 @@
         <v>1065</v>
       </c>
       <c r="C533" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="534" ht="22.5" customHeight="1">
@@ -10601,7 +10631,7 @@
         <v>1067</v>
       </c>
       <c r="C534" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="535" ht="22.5" customHeight="1">
@@ -10612,7 +10642,7 @@
         <v>1069</v>
       </c>
       <c r="C535" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="536" ht="22.5" customHeight="1">
@@ -10623,7 +10653,7 @@
         <v>1071</v>
       </c>
       <c r="C536" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="537" ht="22.5" customHeight="1">
@@ -10634,7 +10664,7 @@
         <v>1073</v>
       </c>
       <c r="C537" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="538" ht="22.5" customHeight="1">
@@ -10645,7 +10675,7 @@
         <v>1075</v>
       </c>
       <c r="C538" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="539" ht="22.5" customHeight="1">
@@ -10656,7 +10686,7 @@
         <v>1077</v>
       </c>
       <c r="C539" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="540" ht="22.5" customHeight="1">
@@ -10667,7 +10697,7 @@
         <v>1079</v>
       </c>
       <c r="C540" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="541" ht="22.5" customHeight="1">
@@ -10678,7 +10708,7 @@
         <v>1081</v>
       </c>
       <c r="C541" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="542" ht="22.5" customHeight="1">
@@ -10689,7 +10719,7 @@
         <v>1083</v>
       </c>
       <c r="C542" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="543" ht="22.5" customHeight="1">
@@ -10700,7 +10730,7 @@
         <v>1085</v>
       </c>
       <c r="C543" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="544" ht="22.5" customHeight="1">
@@ -10711,7 +10741,7 @@
         <v>1087</v>
       </c>
       <c r="C544" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="545" ht="22.5" customHeight="1">
@@ -10722,7 +10752,7 @@
         <v>1089</v>
       </c>
       <c r="C545" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="546" ht="22.5" customHeight="1">
@@ -10733,7 +10763,7 @@
         <v>1091</v>
       </c>
       <c r="C546" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="547" ht="22.5" customHeight="1">
@@ -10744,7 +10774,7 @@
         <v>1093</v>
       </c>
       <c r="C547" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="548" ht="22.5" customHeight="1">
@@ -10755,7 +10785,7 @@
         <v>1095</v>
       </c>
       <c r="C548" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="549" ht="22.5" customHeight="1">
@@ -10766,7 +10796,7 @@
         <v>1097</v>
       </c>
       <c r="C549" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="550" ht="22.5" customHeight="1">
@@ -10777,7 +10807,7 @@
         <v>1099</v>
       </c>
       <c r="C550" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="551" ht="22.5" customHeight="1">
@@ -10788,7 +10818,7 @@
         <v>1101</v>
       </c>
       <c r="C551" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="552" ht="22.5" customHeight="1">
@@ -10799,7 +10829,7 @@
         <v>1103</v>
       </c>
       <c r="C552" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="553" ht="22.5" customHeight="1">
@@ -10810,7 +10840,7 @@
         <v>1105</v>
       </c>
       <c r="C553" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="554" ht="22.5" customHeight="1">
@@ -10821,7 +10851,7 @@
         <v>1107</v>
       </c>
       <c r="C554" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="555" ht="22.5" customHeight="1">
@@ -10832,7 +10862,7 @@
         <v>1109</v>
       </c>
       <c r="C555" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="556" ht="22.5" customHeight="1">
@@ -10843,7 +10873,7 @@
         <v>1111</v>
       </c>
       <c r="C556" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="557" ht="22.5" customHeight="1">
@@ -10854,7 +10884,7 @@
         <v>1113</v>
       </c>
       <c r="C557" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="558" ht="22.5" customHeight="1">
@@ -10865,7 +10895,7 @@
         <v>1115</v>
       </c>
       <c r="C558" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="559" ht="22.5" customHeight="1">
@@ -10876,7 +10906,7 @@
         <v>1117</v>
       </c>
       <c r="C559" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="560" ht="22.5" customHeight="1">
@@ -10887,7 +10917,7 @@
         <v>1119</v>
       </c>
       <c r="C560" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="561" ht="22.5" customHeight="1">
@@ -10898,7 +10928,7 @@
         <v>1121</v>
       </c>
       <c r="C561" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="562" ht="22.5" customHeight="1">
@@ -10909,7 +10939,7 @@
         <v>1123</v>
       </c>
       <c r="C562" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="563" ht="22.5" customHeight="1">
@@ -10920,7 +10950,7 @@
         <v>1125</v>
       </c>
       <c r="C563" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="564" ht="22.5" customHeight="1">
@@ -10931,7 +10961,7 @@
         <v>1127</v>
       </c>
       <c r="C564" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="565" ht="22.5" customHeight="1">
@@ -10942,7 +10972,7 @@
         <v>1129</v>
       </c>
       <c r="C565" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="566" ht="22.5" customHeight="1">
@@ -10953,7 +10983,7 @@
         <v>1131</v>
       </c>
       <c r="C566" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="567" ht="22.5" customHeight="1">
@@ -10964,7 +10994,7 @@
         <v>1133</v>
       </c>
       <c r="C567" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="568" ht="22.5" customHeight="1">
@@ -10975,7 +11005,7 @@
         <v>1135</v>
       </c>
       <c r="C568" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="569" ht="22.5" customHeight="1">
@@ -10986,7 +11016,7 @@
         <v>1137</v>
       </c>
       <c r="C569" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="570" ht="22.5" customHeight="1">
@@ -10997,7 +11027,7 @@
         <v>1139</v>
       </c>
       <c r="C570" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="571" ht="22.5" customHeight="1">
@@ -11008,7 +11038,7 @@
         <v>1141</v>
       </c>
       <c r="C571" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="572" ht="22.5" customHeight="1">
@@ -11019,7 +11049,7 @@
         <v>1143</v>
       </c>
       <c r="C572" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="573" ht="22.5" customHeight="1">
@@ -11030,7 +11060,7 @@
         <v>1145</v>
       </c>
       <c r="C573" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="574" ht="22.5" customHeight="1">
@@ -11041,7 +11071,7 @@
         <v>1147</v>
       </c>
       <c r="C574" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="575" ht="22.5" customHeight="1">
@@ -11052,7 +11082,7 @@
         <v>1149</v>
       </c>
       <c r="C575" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="576" ht="22.5" customHeight="1">
@@ -11063,7 +11093,7 @@
         <v>1151</v>
       </c>
       <c r="C576" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="577" ht="22.5" customHeight="1">
@@ -11074,7 +11104,7 @@
         <v>1153</v>
       </c>
       <c r="C577" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="578" ht="22.5" customHeight="1">
@@ -11085,7 +11115,7 @@
         <v>1155</v>
       </c>
       <c r="C578" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="579" ht="22.5" customHeight="1">
@@ -11096,7 +11126,7 @@
         <v>1157</v>
       </c>
       <c r="C579" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="580" ht="22.5" customHeight="1">
@@ -11107,7 +11137,7 @@
         <v>1159</v>
       </c>
       <c r="C580" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="581" ht="22.5" customHeight="1">
@@ -11118,7 +11148,7 @@
         <v>1161</v>
       </c>
       <c r="C581" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="582" ht="22.5" customHeight="1">
@@ -11129,7 +11159,7 @@
         <v>1163</v>
       </c>
       <c r="C582" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="583" ht="22.5" customHeight="1">
@@ -11140,7 +11170,7 @@
         <v>1165</v>
       </c>
       <c r="C583" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="584" ht="22.5" customHeight="1">
@@ -11151,7 +11181,7 @@
         <v>1167</v>
       </c>
       <c r="C584" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="585" ht="22.5" customHeight="1">
@@ -11162,7 +11192,7 @@
         <v>1169</v>
       </c>
       <c r="C585" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="586" ht="22.5" customHeight="1">
@@ -11173,7 +11203,7 @@
         <v>1171</v>
       </c>
       <c r="C586" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="587" ht="22.5" customHeight="1">
@@ -11184,7 +11214,7 @@
         <v>1173</v>
       </c>
       <c r="C587" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="588" ht="22.5" customHeight="1">
@@ -11195,7 +11225,7 @@
         <v>1175</v>
       </c>
       <c r="C588" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="589" ht="22.5" customHeight="1">
@@ -11206,7 +11236,7 @@
         <v>1177</v>
       </c>
       <c r="C589" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="590" ht="22.5" customHeight="1">
@@ -11217,7 +11247,7 @@
         <v>1179</v>
       </c>
       <c r="C590" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="591" ht="22.5" customHeight="1">
@@ -11228,7 +11258,7 @@
         <v>1181</v>
       </c>
       <c r="C591" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="592" ht="22.5" customHeight="1">
@@ -11239,7 +11269,7 @@
         <v>1183</v>
       </c>
       <c r="C592" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="593" ht="22.5" customHeight="1">
@@ -11250,7 +11280,7 @@
         <v>1185</v>
       </c>
       <c r="C593" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="594" ht="22.5" customHeight="1">
@@ -11261,7 +11291,7 @@
         <v>1187</v>
       </c>
       <c r="C594" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="595" ht="22.5" customHeight="1">
@@ -11272,7 +11302,7 @@
         <v>1189</v>
       </c>
       <c r="C595" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="596" ht="22.5" customHeight="1">
@@ -11283,7 +11313,7 @@
         <v>1191</v>
       </c>
       <c r="C596" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="597" ht="22.5" customHeight="1">
@@ -11294,7 +11324,7 @@
         <v>1193</v>
       </c>
       <c r="C597" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="598" ht="22.5" customHeight="1">
@@ -11305,7 +11335,7 @@
         <v>1195</v>
       </c>
       <c r="C598" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="599" ht="22.5" customHeight="1">
@@ -11316,7 +11346,7 @@
         <v>1197</v>
       </c>
       <c r="C599" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="600" ht="22.5" customHeight="1">
@@ -11327,7 +11357,7 @@
         <v>1199</v>
       </c>
       <c r="C600" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="601" ht="22.5" customHeight="1">
@@ -11338,7 +11368,7 @@
         <v>1201</v>
       </c>
       <c r="C601" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="602" ht="22.5" customHeight="1">
@@ -11349,7 +11379,7 @@
         <v>1203</v>
       </c>
       <c r="C602" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="603" ht="22.5" customHeight="1">
@@ -11360,7 +11390,7 @@
         <v>1205</v>
       </c>
       <c r="C603" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="604" ht="22.5" customHeight="1">
@@ -11371,7 +11401,7 @@
         <v>1207</v>
       </c>
       <c r="C604" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="605" ht="22.5" customHeight="1">
@@ -11382,7 +11412,7 @@
         <v>1209</v>
       </c>
       <c r="C605" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="606" ht="22.5" customHeight="1">
@@ -11393,7 +11423,7 @@
         <v>1211</v>
       </c>
       <c r="C606" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="607" ht="22.5" customHeight="1">
@@ -11404,7 +11434,7 @@
         <v>1213</v>
       </c>
       <c r="C607" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="608" ht="22.5" customHeight="1">
@@ -11415,7 +11445,7 @@
         <v>1215</v>
       </c>
       <c r="C608" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="609" ht="22.5" customHeight="1">
@@ -11426,7 +11456,7 @@
         <v>1217</v>
       </c>
       <c r="C609" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="610" ht="22.5" customHeight="1">
@@ -11437,7 +11467,7 @@
         <v>1219</v>
       </c>
       <c r="C610" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="611" ht="22.5" customHeight="1">
@@ -11448,7 +11478,7 @@
         <v>1221</v>
       </c>
       <c r="C611" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="612" ht="22.5" customHeight="1">
@@ -11459,7 +11489,7 @@
         <v>1223</v>
       </c>
       <c r="C612" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="613" ht="22.5" customHeight="1">
@@ -11470,7 +11500,7 @@
         <v>1225</v>
       </c>
       <c r="C613" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="614" ht="22.5" customHeight="1">
@@ -11481,7 +11511,7 @@
         <v>1227</v>
       </c>
       <c r="C614" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="615" ht="22.5" customHeight="1">
@@ -11492,7 +11522,7 @@
         <v>1229</v>
       </c>
       <c r="C615" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="616" ht="22.5" customHeight="1">
@@ -11503,7 +11533,7 @@
         <v>1231</v>
       </c>
       <c r="C616" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="617" ht="22.5" customHeight="1">
@@ -11514,7 +11544,7 @@
         <v>1233</v>
       </c>
       <c r="C617" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="618" ht="22.5" customHeight="1">
@@ -11525,7 +11555,7 @@
         <v>1235</v>
       </c>
       <c r="C618" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="619" ht="22.5" customHeight="1">
@@ -11536,7 +11566,7 @@
         <v>1237</v>
       </c>
       <c r="C619" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="620" ht="22.5" customHeight="1">
@@ -11547,7 +11577,7 @@
         <v>1239</v>
       </c>
       <c r="C620" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="621" ht="22.5" customHeight="1">
@@ -11558,7 +11588,7 @@
         <v>1241</v>
       </c>
       <c r="C621" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="622" ht="22.5" customHeight="1">
@@ -11569,7 +11599,7 @@
         <v>1243</v>
       </c>
       <c r="C622" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="623" ht="22.5" customHeight="1">
@@ -11580,7 +11610,7 @@
         <v>1245</v>
       </c>
       <c r="C623" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="624" ht="22.5" customHeight="1">
@@ -11591,7 +11621,7 @@
         <v>1247</v>
       </c>
       <c r="C624" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="625" ht="22.5" customHeight="1">
@@ -11602,7 +11632,7 @@
         <v>1249</v>
       </c>
       <c r="C625" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="626" ht="22.5" customHeight="1">
@@ -11613,7 +11643,7 @@
         <v>1251</v>
       </c>
       <c r="C626" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="627" ht="22.5" customHeight="1">
@@ -11624,7 +11654,7 @@
         <v>1253</v>
       </c>
       <c r="C627" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="628" ht="22.5" customHeight="1">
@@ -11635,7 +11665,7 @@
         <v>1255</v>
       </c>
       <c r="C628" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="629" ht="22.5" customHeight="1">
@@ -11646,7 +11676,7 @@
         <v>1257</v>
       </c>
       <c r="C629" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="630" ht="22.5" customHeight="1">
@@ -11657,7 +11687,7 @@
         <v>1259</v>
       </c>
       <c r="C630" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="631" ht="22.5" customHeight="1">
@@ -11668,7 +11698,7 @@
         <v>1261</v>
       </c>
       <c r="C631" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="632" ht="22.5" customHeight="1">
@@ -11679,7 +11709,7 @@
         <v>1263</v>
       </c>
       <c r="C632" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="633" ht="22.5" customHeight="1">
@@ -11690,7 +11720,7 @@
         <v>1265</v>
       </c>
       <c r="C633" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="634" ht="22.5" customHeight="1">
@@ -11701,7 +11731,7 @@
         <v>1267</v>
       </c>
       <c r="C634" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="635" ht="22.5" customHeight="1">
@@ -11712,7 +11742,7 @@
         <v>1269</v>
       </c>
       <c r="C635" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="636" ht="22.5" customHeight="1">
@@ -11723,7 +11753,7 @@
         <v>1271</v>
       </c>
       <c r="C636" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="637" ht="22.5" customHeight="1">
@@ -11734,7 +11764,7 @@
         <v>1273</v>
       </c>
       <c r="C637" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="638" ht="22.5" customHeight="1">
@@ -11745,7 +11775,7 @@
         <v>1275</v>
       </c>
       <c r="C638" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="639" ht="22.5" customHeight="1">
@@ -11756,7 +11786,7 @@
         <v>1277</v>
       </c>
       <c r="C639" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="640" ht="22.5" customHeight="1">
@@ -11767,7 +11797,7 @@
         <v>1279</v>
       </c>
       <c r="C640" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="641" ht="22.5" customHeight="1">
@@ -11778,7 +11808,7 @@
         <v>1281</v>
       </c>
       <c r="C641" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="642" ht="22.5" customHeight="1">
@@ -11789,7 +11819,7 @@
         <v>1283</v>
       </c>
       <c r="C642" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="643" ht="22.5" customHeight="1">
@@ -11800,7 +11830,7 @@
         <v>1285</v>
       </c>
       <c r="C643" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="644" ht="22.5" customHeight="1">
@@ -11811,7 +11841,7 @@
         <v>1287</v>
       </c>
       <c r="C644" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="645" ht="22.5" customHeight="1">
@@ -11822,7 +11852,7 @@
         <v>1289</v>
       </c>
       <c r="C645" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="646" ht="22.5" customHeight="1">
@@ -11833,7 +11863,7 @@
         <v>1291</v>
       </c>
       <c r="C646" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="647" ht="22.5" customHeight="1">
@@ -11844,7 +11874,7 @@
         <v>1293</v>
       </c>
       <c r="C647" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="648" ht="22.5" customHeight="1">
@@ -11855,7 +11885,7 @@
         <v>1295</v>
       </c>
       <c r="C648" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="649" ht="22.5" customHeight="1">
@@ -11866,7 +11896,7 @@
         <v>1297</v>
       </c>
       <c r="C649" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="650" ht="22.5" customHeight="1">
@@ -11877,7 +11907,7 @@
         <v>1299</v>
       </c>
       <c r="C650" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="651" ht="22.5" customHeight="1">
@@ -11888,7 +11918,7 @@
         <v>1301</v>
       </c>
       <c r="C651" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="652" ht="22.5" customHeight="1">
@@ -11899,7 +11929,7 @@
         <v>1303</v>
       </c>
       <c r="C652" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="653" ht="22.5" customHeight="1">
@@ -11910,7 +11940,7 @@
         <v>1305</v>
       </c>
       <c r="C653" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="654" ht="22.5" customHeight="1">
@@ -11921,7 +11951,7 @@
         <v>1307</v>
       </c>
       <c r="C654" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="655" ht="22.5" customHeight="1">
@@ -11932,7 +11962,7 @@
         <v>1309</v>
       </c>
       <c r="C655" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="656" ht="22.5" customHeight="1">
@@ -11943,7 +11973,7 @@
         <v>1311</v>
       </c>
       <c r="C656" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="657" ht="22.5" customHeight="1">
@@ -11954,7 +11984,7 @@
         <v>1313</v>
       </c>
       <c r="C657" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="658" ht="22.5" customHeight="1">
@@ -11965,7 +11995,7 @@
         <v>1315</v>
       </c>
       <c r="C658" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="659" ht="22.5" customHeight="1">
@@ -11976,7 +12006,7 @@
         <v>1317</v>
       </c>
       <c r="C659" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="660" ht="22.5" customHeight="1">
@@ -11987,7 +12017,7 @@
         <v>1319</v>
       </c>
       <c r="C660" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="661" ht="22.5" customHeight="1">
@@ -11998,7 +12028,7 @@
         <v>1215</v>
       </c>
       <c r="C661" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="662" ht="22.5" customHeight="1">
@@ -12009,7 +12039,7 @@
         <v>1322</v>
       </c>
       <c r="C662" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="663" ht="22.5" customHeight="1">
@@ -12020,7 +12050,7 @@
         <v>1324</v>
       </c>
       <c r="C663" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="664" ht="22.5" customHeight="1">
@@ -12031,7 +12061,7 @@
         <v>1326</v>
       </c>
       <c r="C664" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="665" ht="22.5" customHeight="1">
@@ -12042,7 +12072,7 @@
         <v>1328</v>
       </c>
       <c r="C665" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="666" ht="22.5" customHeight="1">
@@ -12053,7 +12083,7 @@
         <v>1330</v>
       </c>
       <c r="C666" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="667" ht="22.5" customHeight="1">
@@ -12064,7 +12094,7 @@
         <v>1332</v>
       </c>
       <c r="C667" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="668" ht="22.5" customHeight="1">
@@ -12075,7 +12105,7 @@
         <v>1334</v>
       </c>
       <c r="C668" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="669" ht="22.5" customHeight="1">
@@ -12086,7 +12116,7 @@
         <v>1336</v>
       </c>
       <c r="C669" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="670" ht="22.5" customHeight="1">
@@ -12097,7 +12127,7 @@
         <v>1338</v>
       </c>
       <c r="C670" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="671" ht="22.5" customHeight="1">
@@ -12108,7 +12138,7 @@
         <v>1340</v>
       </c>
       <c r="C671" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="672" ht="22.5" customHeight="1">
@@ -12119,7 +12149,7 @@
         <v>1342</v>
       </c>
       <c r="C672" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="673" ht="22.5" customHeight="1">
@@ -12130,7 +12160,7 @@
         <v>1344</v>
       </c>
       <c r="C673" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="674" ht="22.5" customHeight="1">
@@ -12141,7 +12171,7 @@
         <v>1346</v>
       </c>
       <c r="C674" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="675" ht="22.5" customHeight="1">
@@ -12152,7 +12182,7 @@
         <v>1348</v>
       </c>
       <c r="C675" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="676" ht="22.5" customHeight="1">
@@ -12163,7 +12193,7 @@
         <v>1350</v>
       </c>
       <c r="C676" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="677" ht="22.5" customHeight="1">
@@ -12174,7 +12204,7 @@
         <v>1352</v>
       </c>
       <c r="C677" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="678" ht="22.5" customHeight="1">
@@ -12185,7 +12215,7 @@
         <v>1354</v>
       </c>
       <c r="C678" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="679" ht="22.5" customHeight="1">
@@ -12196,7 +12226,7 @@
         <v>1356</v>
       </c>
       <c r="C679" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="680" ht="22.5" customHeight="1">
@@ -12207,7 +12237,7 @@
         <v>1358</v>
       </c>
       <c r="C680" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="681" ht="22.5" customHeight="1">
@@ -12218,7 +12248,7 @@
         <v>1360</v>
       </c>
       <c r="C681" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="682" ht="22.5" customHeight="1">
@@ -12229,7 +12259,7 @@
         <v>1362</v>
       </c>
       <c r="C682" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="683" ht="22.5" customHeight="1">
@@ -12240,7 +12270,7 @@
         <v>1364</v>
       </c>
       <c r="C683" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="684" ht="22.5" customHeight="1">
@@ -12251,7 +12281,7 @@
         <v>1366</v>
       </c>
       <c r="C684" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="685" ht="22.5" customHeight="1">
@@ -12262,7 +12292,7 @@
         <v>1368</v>
       </c>
       <c r="C685" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="686" ht="22.5" customHeight="1">
@@ -12273,7 +12303,7 @@
         <v>1370</v>
       </c>
       <c r="C686" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="687" ht="22.5" customHeight="1">
@@ -12284,7 +12314,7 @@
         <v>1372</v>
       </c>
       <c r="C687" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="688" ht="22.5" customHeight="1">
@@ -12295,7 +12325,7 @@
         <v>1374</v>
       </c>
       <c r="C688" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="689" ht="22.5" customHeight="1">
@@ -12306,7 +12336,7 @@
         <v>1376</v>
       </c>
       <c r="C689" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="690" ht="22.5" customHeight="1">
@@ -12317,7 +12347,7 @@
         <v>1378</v>
       </c>
       <c r="C690" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="691" ht="22.5" customHeight="1">
@@ -12328,7 +12358,7 @@
         <v>1380</v>
       </c>
       <c r="C691" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="692" ht="22.5" customHeight="1">
@@ -12339,7 +12369,7 @@
         <v>1382</v>
       </c>
       <c r="C692" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="693" ht="22.5" customHeight="1">
@@ -12350,7 +12380,7 @@
         <v>1384</v>
       </c>
       <c r="C693" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="694" ht="22.5" customHeight="1">
@@ -12361,7 +12391,7 @@
         <v>1386</v>
       </c>
       <c r="C694" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="695" ht="22.5" customHeight="1">
@@ -12372,7 +12402,7 @@
         <v>1388</v>
       </c>
       <c r="C695" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="696" ht="22.5" customHeight="1">
@@ -12383,7 +12413,7 @@
         <v>1390</v>
       </c>
       <c r="C696" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="697" ht="22.5" customHeight="1">
@@ -12394,7 +12424,7 @@
         <v>1392</v>
       </c>
       <c r="C697" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="698" ht="22.5" customHeight="1">
@@ -12405,7 +12435,7 @@
         <v>1394</v>
       </c>
       <c r="C698" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="699" ht="22.5" customHeight="1">
@@ -12416,7 +12446,7 @@
         <v>1396</v>
       </c>
       <c r="C699" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="700" ht="22.5" customHeight="1">
@@ -12427,7 +12457,7 @@
         <v>1398</v>
       </c>
       <c r="C700" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="701" ht="22.5" customHeight="1">
@@ -12438,7 +12468,7 @@
         <v>1400</v>
       </c>
       <c r="C701" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="702" ht="22.5" customHeight="1">
@@ -12449,7 +12479,7 @@
         <v>1402</v>
       </c>
       <c r="C702" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="703" ht="22.5" customHeight="1">
@@ -12460,7 +12490,7 @@
         <v>1404</v>
       </c>
       <c r="C703" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="704" ht="22.5" customHeight="1">
@@ -12471,7 +12501,7 @@
         <v>1406</v>
       </c>
       <c r="C704" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="705" ht="22.5" customHeight="1">
@@ -12482,7 +12512,7 @@
         <v>1408</v>
       </c>
       <c r="C705" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="706" ht="22.5" customHeight="1">
@@ -12493,7 +12523,7 @@
         <v>1410</v>
       </c>
       <c r="C706" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="707" ht="22.5" customHeight="1">
@@ -12504,7 +12534,7 @@
         <v>1412</v>
       </c>
       <c r="C707" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="708" ht="22.5" customHeight="1">
@@ -12515,7 +12545,7 @@
         <v>1414</v>
       </c>
       <c r="C708" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="709" ht="22.5" customHeight="1">
@@ -12526,7 +12556,7 @@
         <v>1416</v>
       </c>
       <c r="C709" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="710" ht="22.5" customHeight="1">
@@ -12537,7 +12567,7 @@
         <v>1418</v>
       </c>
       <c r="C710" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="711" ht="22.5" customHeight="1">
@@ -12548,7 +12578,7 @@
         <v>1420</v>
       </c>
       <c r="C711" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="712" ht="22.5" customHeight="1">
@@ -12559,7 +12589,7 @@
         <v>1422</v>
       </c>
       <c r="C712" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="713" ht="22.5" customHeight="1">
@@ -12570,7 +12600,7 @@
         <v>1424</v>
       </c>
       <c r="C713" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="714" ht="22.5" customHeight="1">
@@ -12581,7 +12611,7 @@
         <v>1426</v>
       </c>
       <c r="C714" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="715" ht="22.5" customHeight="1">
@@ -12592,7 +12622,7 @@
         <v>1428</v>
       </c>
       <c r="C715" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="716" ht="22.5" customHeight="1">
@@ -12603,1402 +12633,1402 @@
         <v>1430</v>
       </c>
       <c r="C716" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="717">
-      <c r="A717" s="9"/>
-      <c r="B717" s="10"/>
-      <c r="C717" s="9"/>
+      <c r="A717" s="11"/>
+      <c r="B717" s="12"/>
+      <c r="C717" s="11"/>
     </row>
     <row r="718">
-      <c r="A718" s="9"/>
-      <c r="B718" s="10"/>
-      <c r="C718" s="9"/>
+      <c r="A718" s="11"/>
+      <c r="B718" s="12"/>
+      <c r="C718" s="11"/>
     </row>
     <row r="719">
-      <c r="A719" s="9"/>
-      <c r="B719" s="10"/>
-      <c r="C719" s="9"/>
+      <c r="A719" s="11"/>
+      <c r="B719" s="12"/>
+      <c r="C719" s="11"/>
     </row>
     <row r="720">
-      <c r="A720" s="9"/>
-      <c r="B720" s="10"/>
-      <c r="C720" s="9"/>
+      <c r="A720" s="11"/>
+      <c r="B720" s="12"/>
+      <c r="C720" s="11"/>
     </row>
     <row r="721">
-      <c r="A721" s="9"/>
-      <c r="B721" s="10"/>
-      <c r="C721" s="9"/>
+      <c r="A721" s="11"/>
+      <c r="B721" s="12"/>
+      <c r="C721" s="11"/>
     </row>
     <row r="722">
-      <c r="A722" s="9"/>
-      <c r="B722" s="10"/>
-      <c r="C722" s="9"/>
+      <c r="A722" s="11"/>
+      <c r="B722" s="12"/>
+      <c r="C722" s="11"/>
     </row>
     <row r="723">
-      <c r="A723" s="9"/>
-      <c r="B723" s="10"/>
-      <c r="C723" s="9"/>
+      <c r="A723" s="11"/>
+      <c r="B723" s="12"/>
+      <c r="C723" s="11"/>
     </row>
     <row r="724">
-      <c r="A724" s="9"/>
-      <c r="B724" s="10"/>
-      <c r="C724" s="9"/>
+      <c r="A724" s="11"/>
+      <c r="B724" s="12"/>
+      <c r="C724" s="11"/>
     </row>
     <row r="725">
-      <c r="A725" s="9"/>
-      <c r="B725" s="10"/>
-      <c r="C725" s="9"/>
+      <c r="A725" s="11"/>
+      <c r="B725" s="12"/>
+      <c r="C725" s="11"/>
     </row>
     <row r="726">
-      <c r="A726" s="9"/>
-      <c r="B726" s="10"/>
-      <c r="C726" s="9"/>
+      <c r="A726" s="11"/>
+      <c r="B726" s="12"/>
+      <c r="C726" s="11"/>
     </row>
     <row r="727">
-      <c r="A727" s="9"/>
-      <c r="B727" s="10"/>
-      <c r="C727" s="9"/>
+      <c r="A727" s="11"/>
+      <c r="B727" s="12"/>
+      <c r="C727" s="11"/>
     </row>
     <row r="728">
-      <c r="A728" s="9"/>
-      <c r="B728" s="10"/>
-      <c r="C728" s="9"/>
+      <c r="A728" s="11"/>
+      <c r="B728" s="12"/>
+      <c r="C728" s="11"/>
     </row>
     <row r="729">
-      <c r="A729" s="9"/>
-      <c r="B729" s="10"/>
-      <c r="C729" s="9"/>
+      <c r="A729" s="11"/>
+      <c r="B729" s="12"/>
+      <c r="C729" s="11"/>
     </row>
     <row r="730">
-      <c r="A730" s="9"/>
-      <c r="B730" s="10"/>
-      <c r="C730" s="9"/>
+      <c r="A730" s="11"/>
+      <c r="B730" s="12"/>
+      <c r="C730" s="11"/>
     </row>
     <row r="731">
-      <c r="A731" s="9"/>
-      <c r="B731" s="10"/>
-      <c r="C731" s="9"/>
+      <c r="A731" s="11"/>
+      <c r="B731" s="12"/>
+      <c r="C731" s="11"/>
     </row>
     <row r="732">
-      <c r="A732" s="9"/>
-      <c r="B732" s="10"/>
-      <c r="C732" s="9"/>
+      <c r="A732" s="11"/>
+      <c r="B732" s="12"/>
+      <c r="C732" s="11"/>
     </row>
     <row r="733">
-      <c r="A733" s="9"/>
-      <c r="B733" s="10"/>
-      <c r="C733" s="9"/>
+      <c r="A733" s="11"/>
+      <c r="B733" s="12"/>
+      <c r="C733" s="11"/>
     </row>
     <row r="734">
-      <c r="A734" s="9"/>
-      <c r="B734" s="10"/>
-      <c r="C734" s="9"/>
+      <c r="A734" s="11"/>
+      <c r="B734" s="12"/>
+      <c r="C734" s="11"/>
     </row>
     <row r="735">
-      <c r="A735" s="9"/>
-      <c r="B735" s="10"/>
-      <c r="C735" s="9"/>
+      <c r="A735" s="11"/>
+      <c r="B735" s="12"/>
+      <c r="C735" s="11"/>
     </row>
     <row r="736">
-      <c r="A736" s="9"/>
-      <c r="B736" s="10"/>
-      <c r="C736" s="9"/>
+      <c r="A736" s="11"/>
+      <c r="B736" s="12"/>
+      <c r="C736" s="11"/>
     </row>
     <row r="737">
-      <c r="A737" s="9"/>
-      <c r="B737" s="10"/>
-      <c r="C737" s="9"/>
+      <c r="A737" s="11"/>
+      <c r="B737" s="12"/>
+      <c r="C737" s="11"/>
     </row>
     <row r="738">
-      <c r="A738" s="9"/>
-      <c r="B738" s="10"/>
-      <c r="C738" s="9"/>
+      <c r="A738" s="11"/>
+      <c r="B738" s="12"/>
+      <c r="C738" s="11"/>
     </row>
     <row r="739">
-      <c r="A739" s="9"/>
-      <c r="B739" s="10"/>
-      <c r="C739" s="9"/>
+      <c r="A739" s="11"/>
+      <c r="B739" s="12"/>
+      <c r="C739" s="11"/>
     </row>
     <row r="740">
-      <c r="A740" s="9"/>
-      <c r="B740" s="10"/>
-      <c r="C740" s="9"/>
+      <c r="A740" s="11"/>
+      <c r="B740" s="12"/>
+      <c r="C740" s="11"/>
     </row>
     <row r="741">
-      <c r="A741" s="9"/>
-      <c r="B741" s="10"/>
-      <c r="C741" s="9"/>
+      <c r="A741" s="11"/>
+      <c r="B741" s="12"/>
+      <c r="C741" s="11"/>
     </row>
     <row r="742">
-      <c r="A742" s="9"/>
-      <c r="B742" s="10"/>
-      <c r="C742" s="9"/>
+      <c r="A742" s="11"/>
+      <c r="B742" s="12"/>
+      <c r="C742" s="11"/>
     </row>
     <row r="743">
-      <c r="A743" s="9"/>
-      <c r="B743" s="10"/>
-      <c r="C743" s="9"/>
+      <c r="A743" s="11"/>
+      <c r="B743" s="12"/>
+      <c r="C743" s="11"/>
     </row>
     <row r="744">
-      <c r="A744" s="9"/>
-      <c r="B744" s="10"/>
-      <c r="C744" s="9"/>
+      <c r="A744" s="11"/>
+      <c r="B744" s="12"/>
+      <c r="C744" s="11"/>
     </row>
     <row r="745">
-      <c r="A745" s="9"/>
-      <c r="B745" s="10"/>
-      <c r="C745" s="9"/>
+      <c r="A745" s="11"/>
+      <c r="B745" s="12"/>
+      <c r="C745" s="11"/>
     </row>
     <row r="746">
-      <c r="A746" s="9"/>
-      <c r="B746" s="10"/>
-      <c r="C746" s="9"/>
+      <c r="A746" s="11"/>
+      <c r="B746" s="12"/>
+      <c r="C746" s="11"/>
     </row>
     <row r="747">
-      <c r="A747" s="9"/>
-      <c r="B747" s="10"/>
-      <c r="C747" s="9"/>
+      <c r="A747" s="11"/>
+      <c r="B747" s="12"/>
+      <c r="C747" s="11"/>
     </row>
     <row r="748">
-      <c r="A748" s="9"/>
-      <c r="B748" s="10"/>
-      <c r="C748" s="9"/>
+      <c r="A748" s="11"/>
+      <c r="B748" s="12"/>
+      <c r="C748" s="11"/>
     </row>
     <row r="749">
-      <c r="A749" s="9"/>
-      <c r="B749" s="10"/>
-      <c r="C749" s="9"/>
+      <c r="A749" s="11"/>
+      <c r="B749" s="12"/>
+      <c r="C749" s="11"/>
     </row>
     <row r="750">
-      <c r="A750" s="9"/>
-      <c r="B750" s="10"/>
-      <c r="C750" s="9"/>
+      <c r="A750" s="11"/>
+      <c r="B750" s="12"/>
+      <c r="C750" s="11"/>
     </row>
     <row r="751">
-      <c r="A751" s="9"/>
-      <c r="B751" s="10"/>
-      <c r="C751" s="9"/>
+      <c r="A751" s="11"/>
+      <c r="B751" s="12"/>
+      <c r="C751" s="11"/>
     </row>
     <row r="752">
-      <c r="A752" s="9"/>
-      <c r="B752" s="10"/>
-      <c r="C752" s="9"/>
+      <c r="A752" s="11"/>
+      <c r="B752" s="12"/>
+      <c r="C752" s="11"/>
     </row>
     <row r="753">
-      <c r="A753" s="9"/>
-      <c r="B753" s="10"/>
-      <c r="C753" s="9"/>
+      <c r="A753" s="11"/>
+      <c r="B753" s="12"/>
+      <c r="C753" s="11"/>
     </row>
     <row r="754">
-      <c r="A754" s="9"/>
-      <c r="B754" s="10"/>
-      <c r="C754" s="9"/>
+      <c r="A754" s="11"/>
+      <c r="B754" s="12"/>
+      <c r="C754" s="11"/>
     </row>
     <row r="755">
-      <c r="A755" s="9"/>
-      <c r="B755" s="10"/>
-      <c r="C755" s="9"/>
+      <c r="A755" s="11"/>
+      <c r="B755" s="12"/>
+      <c r="C755" s="11"/>
     </row>
     <row r="756">
-      <c r="A756" s="9"/>
-      <c r="B756" s="10"/>
-      <c r="C756" s="9"/>
+      <c r="A756" s="11"/>
+      <c r="B756" s="12"/>
+      <c r="C756" s="11"/>
     </row>
     <row r="757">
-      <c r="A757" s="9"/>
-      <c r="B757" s="10"/>
-      <c r="C757" s="9"/>
+      <c r="A757" s="11"/>
+      <c r="B757" s="12"/>
+      <c r="C757" s="11"/>
     </row>
     <row r="758">
-      <c r="A758" s="9"/>
-      <c r="B758" s="10"/>
-      <c r="C758" s="9"/>
+      <c r="A758" s="11"/>
+      <c r="B758" s="12"/>
+      <c r="C758" s="11"/>
     </row>
     <row r="759">
-      <c r="A759" s="9"/>
-      <c r="B759" s="10"/>
-      <c r="C759" s="9"/>
+      <c r="A759" s="11"/>
+      <c r="B759" s="12"/>
+      <c r="C759" s="11"/>
     </row>
     <row r="760">
-      <c r="A760" s="9"/>
-      <c r="B760" s="10"/>
-      <c r="C760" s="9"/>
+      <c r="A760" s="11"/>
+      <c r="B760" s="12"/>
+      <c r="C760" s="11"/>
     </row>
     <row r="761">
-      <c r="A761" s="9"/>
-      <c r="B761" s="10"/>
-      <c r="C761" s="9"/>
+      <c r="A761" s="11"/>
+      <c r="B761" s="12"/>
+      <c r="C761" s="11"/>
     </row>
     <row r="762">
-      <c r="A762" s="9"/>
-      <c r="B762" s="10"/>
-      <c r="C762" s="9"/>
+      <c r="A762" s="11"/>
+      <c r="B762" s="12"/>
+      <c r="C762" s="11"/>
     </row>
     <row r="763">
-      <c r="A763" s="9"/>
-      <c r="B763" s="10"/>
-      <c r="C763" s="9"/>
+      <c r="A763" s="11"/>
+      <c r="B763" s="12"/>
+      <c r="C763" s="11"/>
     </row>
     <row r="764">
-      <c r="A764" s="9"/>
-      <c r="B764" s="10"/>
-      <c r="C764" s="9"/>
+      <c r="A764" s="11"/>
+      <c r="B764" s="12"/>
+      <c r="C764" s="11"/>
     </row>
     <row r="765">
-      <c r="A765" s="9"/>
-      <c r="B765" s="10"/>
-      <c r="C765" s="9"/>
+      <c r="A765" s="11"/>
+      <c r="B765" s="12"/>
+      <c r="C765" s="11"/>
     </row>
     <row r="766">
-      <c r="A766" s="9"/>
-      <c r="B766" s="10"/>
-      <c r="C766" s="9"/>
+      <c r="A766" s="11"/>
+      <c r="B766" s="12"/>
+      <c r="C766" s="11"/>
     </row>
     <row r="767">
-      <c r="A767" s="9"/>
-      <c r="B767" s="10"/>
-      <c r="C767" s="9"/>
+      <c r="A767" s="11"/>
+      <c r="B767" s="12"/>
+      <c r="C767" s="11"/>
     </row>
     <row r="768">
-      <c r="A768" s="9"/>
-      <c r="B768" s="10"/>
-      <c r="C768" s="9"/>
+      <c r="A768" s="11"/>
+      <c r="B768" s="12"/>
+      <c r="C768" s="11"/>
     </row>
     <row r="769">
-      <c r="A769" s="9"/>
-      <c r="B769" s="10"/>
-      <c r="C769" s="9"/>
+      <c r="A769" s="11"/>
+      <c r="B769" s="12"/>
+      <c r="C769" s="11"/>
     </row>
     <row r="770">
-      <c r="A770" s="9"/>
-      <c r="B770" s="10"/>
-      <c r="C770" s="9"/>
+      <c r="A770" s="11"/>
+      <c r="B770" s="12"/>
+      <c r="C770" s="11"/>
     </row>
     <row r="771">
-      <c r="A771" s="9"/>
-      <c r="B771" s="10"/>
-      <c r="C771" s="9"/>
+      <c r="A771" s="11"/>
+      <c r="B771" s="12"/>
+      <c r="C771" s="11"/>
     </row>
     <row r="772">
       <c r="A772" s="3"/>
-      <c r="B772" s="11"/>
+      <c r="B772" s="9"/>
       <c r="C772" s="3"/>
     </row>
     <row r="773">
       <c r="A773" s="3"/>
-      <c r="B773" s="11"/>
+      <c r="B773" s="9"/>
       <c r="C773" s="3"/>
     </row>
     <row r="774">
       <c r="A774" s="3"/>
-      <c r="B774" s="11"/>
+      <c r="B774" s="9"/>
       <c r="C774" s="3"/>
     </row>
     <row r="775">
       <c r="A775" s="3"/>
-      <c r="B775" s="11"/>
+      <c r="B775" s="9"/>
       <c r="C775" s="3"/>
     </row>
     <row r="776">
       <c r="A776" s="3"/>
-      <c r="B776" s="11"/>
+      <c r="B776" s="9"/>
       <c r="C776" s="3"/>
     </row>
     <row r="777">
       <c r="A777" s="3"/>
-      <c r="B777" s="11"/>
+      <c r="B777" s="9"/>
       <c r="C777" s="3"/>
     </row>
     <row r="778">
       <c r="A778" s="3"/>
-      <c r="B778" s="11"/>
+      <c r="B778" s="9"/>
       <c r="C778" s="3"/>
     </row>
     <row r="779">
       <c r="A779" s="3"/>
-      <c r="B779" s="11"/>
+      <c r="B779" s="9"/>
       <c r="C779" s="3"/>
     </row>
     <row r="780">
       <c r="A780" s="3"/>
-      <c r="B780" s="11"/>
+      <c r="B780" s="9"/>
       <c r="C780" s="3"/>
     </row>
     <row r="781">
       <c r="A781" s="3"/>
-      <c r="B781" s="11"/>
+      <c r="B781" s="9"/>
       <c r="C781" s="3"/>
     </row>
     <row r="782">
       <c r="A782" s="3"/>
-      <c r="B782" s="11"/>
+      <c r="B782" s="9"/>
       <c r="C782" s="3"/>
     </row>
     <row r="783">
       <c r="A783" s="3"/>
-      <c r="B783" s="11"/>
+      <c r="B783" s="9"/>
       <c r="C783" s="3"/>
     </row>
     <row r="784">
       <c r="A784" s="3"/>
-      <c r="B784" s="11"/>
+      <c r="B784" s="9"/>
       <c r="C784" s="3"/>
     </row>
     <row r="785">
       <c r="A785" s="3"/>
-      <c r="B785" s="11"/>
+      <c r="B785" s="9"/>
       <c r="C785" s="3"/>
     </row>
     <row r="786">
       <c r="A786" s="3"/>
-      <c r="B786" s="11"/>
+      <c r="B786" s="9"/>
       <c r="C786" s="3"/>
     </row>
     <row r="787">
       <c r="A787" s="3"/>
-      <c r="B787" s="11"/>
+      <c r="B787" s="9"/>
       <c r="C787" s="3"/>
     </row>
     <row r="788">
       <c r="A788" s="3"/>
-      <c r="B788" s="11"/>
+      <c r="B788" s="9"/>
       <c r="C788" s="3"/>
     </row>
     <row r="789">
       <c r="A789" s="3"/>
-      <c r="B789" s="11"/>
+      <c r="B789" s="9"/>
       <c r="C789" s="3"/>
     </row>
     <row r="790">
       <c r="A790" s="3"/>
-      <c r="B790" s="11"/>
+      <c r="B790" s="9"/>
       <c r="C790" s="3"/>
     </row>
     <row r="791">
       <c r="A791" s="3"/>
-      <c r="B791" s="11"/>
+      <c r="B791" s="9"/>
       <c r="C791" s="3"/>
     </row>
     <row r="792">
       <c r="A792" s="3"/>
-      <c r="B792" s="11"/>
+      <c r="B792" s="9"/>
       <c r="C792" s="3"/>
     </row>
     <row r="793">
       <c r="A793" s="3"/>
-      <c r="B793" s="11"/>
+      <c r="B793" s="9"/>
       <c r="C793" s="3"/>
     </row>
     <row r="794">
       <c r="A794" s="3"/>
-      <c r="B794" s="11"/>
+      <c r="B794" s="9"/>
       <c r="C794" s="3"/>
     </row>
     <row r="795">
       <c r="A795" s="3"/>
-      <c r="B795" s="11"/>
+      <c r="B795" s="9"/>
       <c r="C795" s="3"/>
     </row>
     <row r="796">
       <c r="A796" s="3"/>
-      <c r="B796" s="11"/>
+      <c r="B796" s="9"/>
       <c r="C796" s="3"/>
     </row>
     <row r="797">
       <c r="A797" s="3"/>
-      <c r="B797" s="11"/>
+      <c r="B797" s="9"/>
       <c r="C797" s="3"/>
     </row>
     <row r="798">
       <c r="A798" s="3"/>
-      <c r="B798" s="11"/>
+      <c r="B798" s="9"/>
       <c r="C798" s="3"/>
     </row>
     <row r="799">
       <c r="A799" s="3"/>
-      <c r="B799" s="11"/>
+      <c r="B799" s="9"/>
       <c r="C799" s="3"/>
     </row>
     <row r="800">
       <c r="A800" s="3"/>
-      <c r="B800" s="11"/>
+      <c r="B800" s="9"/>
       <c r="C800" s="3"/>
     </row>
     <row r="801">
       <c r="A801" s="3"/>
-      <c r="B801" s="11"/>
+      <c r="B801" s="9"/>
       <c r="C801" s="3"/>
     </row>
     <row r="802">
       <c r="A802" s="3"/>
-      <c r="B802" s="11"/>
+      <c r="B802" s="9"/>
       <c r="C802" s="3"/>
     </row>
     <row r="803">
       <c r="A803" s="3"/>
-      <c r="B803" s="11"/>
+      <c r="B803" s="9"/>
       <c r="C803" s="3"/>
     </row>
     <row r="804">
       <c r="A804" s="3"/>
-      <c r="B804" s="11"/>
+      <c r="B804" s="9"/>
       <c r="C804" s="3"/>
     </row>
     <row r="805">
       <c r="A805" s="3"/>
-      <c r="B805" s="11"/>
+      <c r="B805" s="9"/>
       <c r="C805" s="3"/>
     </row>
     <row r="806">
       <c r="A806" s="3"/>
-      <c r="B806" s="11"/>
+      <c r="B806" s="9"/>
       <c r="C806" s="3"/>
     </row>
     <row r="807">
       <c r="A807" s="3"/>
-      <c r="B807" s="11"/>
+      <c r="B807" s="9"/>
       <c r="C807" s="3"/>
     </row>
     <row r="808">
       <c r="A808" s="3"/>
-      <c r="B808" s="11"/>
+      <c r="B808" s="9"/>
       <c r="C808" s="3"/>
     </row>
     <row r="809">
       <c r="A809" s="3"/>
-      <c r="B809" s="11"/>
+      <c r="B809" s="9"/>
       <c r="C809" s="3"/>
     </row>
     <row r="810">
       <c r="A810" s="3"/>
-      <c r="B810" s="11"/>
+      <c r="B810" s="9"/>
       <c r="C810" s="3"/>
     </row>
     <row r="811">
       <c r="A811" s="3"/>
-      <c r="B811" s="11"/>
+      <c r="B811" s="9"/>
       <c r="C811" s="3"/>
     </row>
     <row r="812">
       <c r="A812" s="3"/>
-      <c r="B812" s="11"/>
+      <c r="B812" s="9"/>
       <c r="C812" s="3"/>
     </row>
     <row r="813">
       <c r="A813" s="3"/>
-      <c r="B813" s="11"/>
+      <c r="B813" s="9"/>
       <c r="C813" s="3"/>
     </row>
     <row r="814">
       <c r="A814" s="3"/>
-      <c r="B814" s="11"/>
+      <c r="B814" s="9"/>
       <c r="C814" s="3"/>
     </row>
     <row r="815">
       <c r="A815" s="3"/>
-      <c r="B815" s="11"/>
+      <c r="B815" s="9"/>
       <c r="C815" s="3"/>
     </row>
     <row r="816">
       <c r="A816" s="3"/>
-      <c r="B816" s="11"/>
+      <c r="B816" s="9"/>
       <c r="C816" s="3"/>
     </row>
     <row r="817">
       <c r="A817" s="3"/>
-      <c r="B817" s="11"/>
+      <c r="B817" s="9"/>
       <c r="C817" s="3"/>
     </row>
     <row r="818">
       <c r="A818" s="3"/>
-      <c r="B818" s="11"/>
+      <c r="B818" s="9"/>
       <c r="C818" s="3"/>
     </row>
     <row r="819">
       <c r="A819" s="3"/>
-      <c r="B819" s="11"/>
+      <c r="B819" s="9"/>
       <c r="C819" s="3"/>
     </row>
     <row r="820">
       <c r="A820" s="3"/>
-      <c r="B820" s="11"/>
+      <c r="B820" s="9"/>
       <c r="C820" s="3"/>
     </row>
     <row r="821">
       <c r="A821" s="3"/>
-      <c r="B821" s="11"/>
+      <c r="B821" s="9"/>
       <c r="C821" s="3"/>
     </row>
     <row r="822">
       <c r="A822" s="3"/>
-      <c r="B822" s="11"/>
+      <c r="B822" s="9"/>
       <c r="C822" s="3"/>
     </row>
     <row r="823">
       <c r="A823" s="3"/>
-      <c r="B823" s="11"/>
+      <c r="B823" s="9"/>
       <c r="C823" s="3"/>
     </row>
     <row r="824">
       <c r="A824" s="3"/>
-      <c r="B824" s="11"/>
+      <c r="B824" s="9"/>
       <c r="C824" s="3"/>
     </row>
     <row r="825">
       <c r="A825" s="3"/>
-      <c r="B825" s="11"/>
+      <c r="B825" s="9"/>
       <c r="C825" s="3"/>
     </row>
     <row r="826">
       <c r="A826" s="3"/>
-      <c r="B826" s="11"/>
+      <c r="B826" s="9"/>
       <c r="C826" s="3"/>
     </row>
     <row r="827">
       <c r="A827" s="3"/>
-      <c r="B827" s="11"/>
+      <c r="B827" s="9"/>
       <c r="C827" s="3"/>
     </row>
     <row r="828">
       <c r="A828" s="3"/>
-      <c r="B828" s="11"/>
+      <c r="B828" s="9"/>
       <c r="C828" s="3"/>
     </row>
     <row r="829">
       <c r="A829" s="3"/>
-      <c r="B829" s="11"/>
+      <c r="B829" s="9"/>
       <c r="C829" s="3"/>
     </row>
     <row r="830">
       <c r="A830" s="3"/>
-      <c r="B830" s="11"/>
+      <c r="B830" s="9"/>
       <c r="C830" s="3"/>
     </row>
     <row r="831">
       <c r="A831" s="3"/>
-      <c r="B831" s="11"/>
+      <c r="B831" s="9"/>
       <c r="C831" s="3"/>
     </row>
     <row r="832">
       <c r="A832" s="3"/>
-      <c r="B832" s="11"/>
+      <c r="B832" s="9"/>
       <c r="C832" s="3"/>
     </row>
     <row r="833">
       <c r="A833" s="3"/>
-      <c r="B833" s="11"/>
+      <c r="B833" s="9"/>
       <c r="C833" s="3"/>
     </row>
     <row r="834">
       <c r="A834" s="3"/>
-      <c r="B834" s="11"/>
+      <c r="B834" s="9"/>
       <c r="C834" s="3"/>
     </row>
     <row r="835">
       <c r="A835" s="3"/>
-      <c r="B835" s="11"/>
+      <c r="B835" s="9"/>
       <c r="C835" s="3"/>
     </row>
     <row r="836">
       <c r="A836" s="3"/>
-      <c r="B836" s="11"/>
+      <c r="B836" s="9"/>
       <c r="C836" s="3"/>
     </row>
     <row r="837">
       <c r="A837" s="3"/>
-      <c r="B837" s="11"/>
+      <c r="B837" s="9"/>
       <c r="C837" s="3"/>
     </row>
     <row r="838">
       <c r="A838" s="3"/>
-      <c r="B838" s="11"/>
+      <c r="B838" s="9"/>
       <c r="C838" s="3"/>
     </row>
     <row r="839">
       <c r="A839" s="3"/>
-      <c r="B839" s="11"/>
+      <c r="B839" s="9"/>
       <c r="C839" s="3"/>
     </row>
     <row r="840">
       <c r="A840" s="3"/>
-      <c r="B840" s="11"/>
+      <c r="B840" s="9"/>
       <c r="C840" s="3"/>
     </row>
     <row r="841">
       <c r="A841" s="3"/>
-      <c r="B841" s="11"/>
+      <c r="B841" s="9"/>
       <c r="C841" s="3"/>
     </row>
     <row r="842">
       <c r="A842" s="3"/>
-      <c r="B842" s="11"/>
+      <c r="B842" s="9"/>
       <c r="C842" s="3"/>
     </row>
     <row r="843">
       <c r="A843" s="3"/>
-      <c r="B843" s="11"/>
+      <c r="B843" s="9"/>
       <c r="C843" s="3"/>
     </row>
     <row r="844">
       <c r="A844" s="3"/>
-      <c r="B844" s="11"/>
+      <c r="B844" s="9"/>
       <c r="C844" s="3"/>
     </row>
     <row r="845">
       <c r="A845" s="3"/>
-      <c r="B845" s="11"/>
+      <c r="B845" s="9"/>
       <c r="C845" s="3"/>
     </row>
     <row r="846">
       <c r="A846" s="3"/>
-      <c r="B846" s="11"/>
+      <c r="B846" s="9"/>
       <c r="C846" s="3"/>
     </row>
     <row r="847">
       <c r="A847" s="3"/>
-      <c r="B847" s="11"/>
+      <c r="B847" s="9"/>
       <c r="C847" s="3"/>
     </row>
     <row r="848">
       <c r="A848" s="3"/>
-      <c r="B848" s="11"/>
+      <c r="B848" s="9"/>
       <c r="C848" s="3"/>
     </row>
     <row r="849">
       <c r="A849" s="3"/>
-      <c r="B849" s="11"/>
+      <c r="B849" s="9"/>
       <c r="C849" s="3"/>
     </row>
     <row r="850">
       <c r="A850" s="3"/>
-      <c r="B850" s="11"/>
+      <c r="B850" s="9"/>
       <c r="C850" s="3"/>
     </row>
     <row r="851">
       <c r="A851" s="3"/>
-      <c r="B851" s="11"/>
+      <c r="B851" s="9"/>
       <c r="C851" s="3"/>
     </row>
     <row r="852">
       <c r="A852" s="3"/>
-      <c r="B852" s="11"/>
+      <c r="B852" s="9"/>
       <c r="C852" s="3"/>
     </row>
     <row r="853">
       <c r="A853" s="3"/>
-      <c r="B853" s="11"/>
+      <c r="B853" s="9"/>
       <c r="C853" s="3"/>
     </row>
     <row r="854">
       <c r="A854" s="3"/>
-      <c r="B854" s="11"/>
+      <c r="B854" s="9"/>
       <c r="C854" s="3"/>
     </row>
     <row r="855">
       <c r="A855" s="3"/>
-      <c r="B855" s="11"/>
+      <c r="B855" s="9"/>
       <c r="C855" s="3"/>
     </row>
     <row r="856">
       <c r="A856" s="3"/>
-      <c r="B856" s="11"/>
+      <c r="B856" s="9"/>
       <c r="C856" s="3"/>
     </row>
     <row r="857">
       <c r="A857" s="3"/>
-      <c r="B857" s="11"/>
+      <c r="B857" s="9"/>
       <c r="C857" s="3"/>
     </row>
     <row r="858">
       <c r="A858" s="3"/>
-      <c r="B858" s="11"/>
+      <c r="B858" s="9"/>
       <c r="C858" s="3"/>
     </row>
     <row r="859">
       <c r="A859" s="3"/>
-      <c r="B859" s="11"/>
+      <c r="B859" s="9"/>
       <c r="C859" s="3"/>
     </row>
     <row r="860">
       <c r="A860" s="3"/>
-      <c r="B860" s="11"/>
+      <c r="B860" s="9"/>
       <c r="C860" s="3"/>
     </row>
     <row r="861">
       <c r="A861" s="3"/>
-      <c r="B861" s="11"/>
+      <c r="B861" s="9"/>
       <c r="C861" s="3"/>
     </row>
     <row r="862">
       <c r="A862" s="3"/>
-      <c r="B862" s="11"/>
+      <c r="B862" s="9"/>
       <c r="C862" s="3"/>
     </row>
     <row r="863">
       <c r="A863" s="3"/>
-      <c r="B863" s="11"/>
+      <c r="B863" s="9"/>
       <c r="C863" s="3"/>
     </row>
     <row r="864">
       <c r="A864" s="3"/>
-      <c r="B864" s="11"/>
+      <c r="B864" s="9"/>
       <c r="C864" s="3"/>
     </row>
     <row r="865">
       <c r="A865" s="3"/>
-      <c r="B865" s="11"/>
+      <c r="B865" s="9"/>
       <c r="C865" s="3"/>
     </row>
     <row r="866">
       <c r="A866" s="3"/>
-      <c r="B866" s="11"/>
+      <c r="B866" s="9"/>
       <c r="C866" s="3"/>
     </row>
     <row r="867">
       <c r="A867" s="3"/>
-      <c r="B867" s="11"/>
+      <c r="B867" s="9"/>
       <c r="C867" s="3"/>
     </row>
     <row r="868">
       <c r="A868" s="3"/>
-      <c r="B868" s="11"/>
+      <c r="B868" s="9"/>
       <c r="C868" s="3"/>
     </row>
     <row r="869">
       <c r="A869" s="3"/>
-      <c r="B869" s="11"/>
+      <c r="B869" s="9"/>
       <c r="C869" s="3"/>
     </row>
     <row r="870">
       <c r="A870" s="3"/>
-      <c r="B870" s="11"/>
+      <c r="B870" s="9"/>
       <c r="C870" s="3"/>
     </row>
     <row r="871">
       <c r="A871" s="3"/>
-      <c r="B871" s="11"/>
+      <c r="B871" s="9"/>
       <c r="C871" s="3"/>
     </row>
     <row r="872">
       <c r="A872" s="3"/>
-      <c r="B872" s="11"/>
+      <c r="B872" s="9"/>
       <c r="C872" s="3"/>
     </row>
     <row r="873">
       <c r="A873" s="3"/>
-      <c r="B873" s="11"/>
+      <c r="B873" s="9"/>
       <c r="C873" s="3"/>
     </row>
     <row r="874">
       <c r="A874" s="3"/>
-      <c r="B874" s="11"/>
+      <c r="B874" s="9"/>
       <c r="C874" s="3"/>
     </row>
     <row r="875">
       <c r="A875" s="3"/>
-      <c r="B875" s="11"/>
+      <c r="B875" s="9"/>
       <c r="C875" s="3"/>
     </row>
     <row r="876">
       <c r="A876" s="3"/>
-      <c r="B876" s="11"/>
+      <c r="B876" s="9"/>
       <c r="C876" s="3"/>
     </row>
     <row r="877">
       <c r="A877" s="3"/>
-      <c r="B877" s="11"/>
+      <c r="B877" s="9"/>
       <c r="C877" s="3"/>
     </row>
     <row r="878">
       <c r="A878" s="3"/>
-      <c r="B878" s="11"/>
+      <c r="B878" s="9"/>
       <c r="C878" s="3"/>
     </row>
     <row r="879">
       <c r="A879" s="3"/>
-      <c r="B879" s="11"/>
+      <c r="B879" s="9"/>
       <c r="C879" s="3"/>
     </row>
     <row r="880">
       <c r="A880" s="3"/>
-      <c r="B880" s="11"/>
+      <c r="B880" s="9"/>
       <c r="C880" s="3"/>
     </row>
     <row r="881">
       <c r="A881" s="3"/>
-      <c r="B881" s="11"/>
+      <c r="B881" s="9"/>
       <c r="C881" s="3"/>
     </row>
     <row r="882">
       <c r="A882" s="3"/>
-      <c r="B882" s="11"/>
+      <c r="B882" s="9"/>
       <c r="C882" s="3"/>
     </row>
     <row r="883">
       <c r="A883" s="3"/>
-      <c r="B883" s="11"/>
+      <c r="B883" s="9"/>
       <c r="C883" s="3"/>
     </row>
     <row r="884">
       <c r="A884" s="3"/>
-      <c r="B884" s="11"/>
+      <c r="B884" s="9"/>
       <c r="C884" s="3"/>
     </row>
     <row r="885">
       <c r="A885" s="3"/>
-      <c r="B885" s="11"/>
+      <c r="B885" s="9"/>
       <c r="C885" s="3"/>
     </row>
     <row r="886">
       <c r="A886" s="3"/>
-      <c r="B886" s="11"/>
+      <c r="B886" s="9"/>
       <c r="C886" s="3"/>
     </row>
     <row r="887">
       <c r="A887" s="3"/>
-      <c r="B887" s="11"/>
+      <c r="B887" s="9"/>
       <c r="C887" s="3"/>
     </row>
     <row r="888">
       <c r="A888" s="3"/>
-      <c r="B888" s="11"/>
+      <c r="B888" s="9"/>
       <c r="C888" s="3"/>
     </row>
     <row r="889">
       <c r="A889" s="3"/>
-      <c r="B889" s="11"/>
+      <c r="B889" s="9"/>
       <c r="C889" s="3"/>
     </row>
     <row r="890">
       <c r="A890" s="3"/>
-      <c r="B890" s="11"/>
+      <c r="B890" s="9"/>
       <c r="C890" s="3"/>
     </row>
     <row r="891">
       <c r="A891" s="3"/>
-      <c r="B891" s="11"/>
+      <c r="B891" s="9"/>
       <c r="C891" s="3"/>
     </row>
     <row r="892">
       <c r="A892" s="3"/>
-      <c r="B892" s="11"/>
+      <c r="B892" s="9"/>
       <c r="C892" s="3"/>
     </row>
     <row r="893">
       <c r="A893" s="3"/>
-      <c r="B893" s="11"/>
+      <c r="B893" s="9"/>
       <c r="C893" s="3"/>
     </row>
     <row r="894">
       <c r="A894" s="3"/>
-      <c r="B894" s="11"/>
+      <c r="B894" s="9"/>
       <c r="C894" s="3"/>
     </row>
     <row r="895">
       <c r="A895" s="3"/>
-      <c r="B895" s="11"/>
+      <c r="B895" s="9"/>
       <c r="C895" s="3"/>
     </row>
     <row r="896">
       <c r="A896" s="3"/>
-      <c r="B896" s="11"/>
+      <c r="B896" s="9"/>
       <c r="C896" s="3"/>
     </row>
     <row r="897">
       <c r="A897" s="3"/>
-      <c r="B897" s="11"/>
+      <c r="B897" s="9"/>
       <c r="C897" s="3"/>
     </row>
     <row r="898">
       <c r="A898" s="3"/>
-      <c r="B898" s="11"/>
+      <c r="B898" s="9"/>
       <c r="C898" s="3"/>
     </row>
     <row r="899">
       <c r="A899" s="3"/>
-      <c r="B899" s="11"/>
+      <c r="B899" s="9"/>
       <c r="C899" s="3"/>
     </row>
     <row r="900">
       <c r="A900" s="3"/>
-      <c r="B900" s="11"/>
+      <c r="B900" s="9"/>
       <c r="C900" s="3"/>
     </row>
     <row r="901">
       <c r="A901" s="3"/>
-      <c r="B901" s="11"/>
+      <c r="B901" s="9"/>
       <c r="C901" s="3"/>
     </row>
     <row r="902">
       <c r="A902" s="3"/>
-      <c r="B902" s="11"/>
+      <c r="B902" s="9"/>
       <c r="C902" s="3"/>
     </row>
     <row r="903">
       <c r="A903" s="3"/>
-      <c r="B903" s="11"/>
+      <c r="B903" s="9"/>
       <c r="C903" s="3"/>
     </row>
     <row r="904">
       <c r="A904" s="3"/>
-      <c r="B904" s="11"/>
+      <c r="B904" s="9"/>
       <c r="C904" s="3"/>
     </row>
     <row r="905">
       <c r="A905" s="3"/>
-      <c r="B905" s="11"/>
+      <c r="B905" s="9"/>
       <c r="C905" s="3"/>
     </row>
     <row r="906">
       <c r="A906" s="3"/>
-      <c r="B906" s="11"/>
+      <c r="B906" s="9"/>
       <c r="C906" s="3"/>
     </row>
     <row r="907">
       <c r="A907" s="3"/>
-      <c r="B907" s="11"/>
+      <c r="B907" s="9"/>
       <c r="C907" s="3"/>
     </row>
     <row r="908">
       <c r="A908" s="3"/>
-      <c r="B908" s="11"/>
+      <c r="B908" s="9"/>
       <c r="C908" s="3"/>
     </row>
     <row r="909">
       <c r="A909" s="3"/>
-      <c r="B909" s="11"/>
+      <c r="B909" s="9"/>
       <c r="C909" s="3"/>
     </row>
     <row r="910">
       <c r="A910" s="3"/>
-      <c r="B910" s="11"/>
+      <c r="B910" s="9"/>
       <c r="C910" s="3"/>
     </row>
     <row r="911">
       <c r="A911" s="3"/>
-      <c r="B911" s="11"/>
+      <c r="B911" s="9"/>
       <c r="C911" s="3"/>
     </row>
     <row r="912">
       <c r="A912" s="3"/>
-      <c r="B912" s="11"/>
+      <c r="B912" s="9"/>
       <c r="C912" s="3"/>
     </row>
     <row r="913">
       <c r="A913" s="3"/>
-      <c r="B913" s="11"/>
+      <c r="B913" s="9"/>
       <c r="C913" s="3"/>
     </row>
     <row r="914">
       <c r="A914" s="3"/>
-      <c r="B914" s="11"/>
+      <c r="B914" s="9"/>
       <c r="C914" s="3"/>
     </row>
     <row r="915">
       <c r="A915" s="3"/>
-      <c r="B915" s="11"/>
+      <c r="B915" s="9"/>
       <c r="C915" s="3"/>
     </row>
     <row r="916">
       <c r="A916" s="3"/>
-      <c r="B916" s="11"/>
+      <c r="B916" s="9"/>
       <c r="C916" s="3"/>
     </row>
     <row r="917">
       <c r="A917" s="3"/>
-      <c r="B917" s="11"/>
+      <c r="B917" s="9"/>
       <c r="C917" s="3"/>
     </row>
     <row r="918">
       <c r="A918" s="3"/>
-      <c r="B918" s="11"/>
+      <c r="B918" s="9"/>
       <c r="C918" s="3"/>
     </row>
     <row r="919">
       <c r="A919" s="3"/>
-      <c r="B919" s="11"/>
+      <c r="B919" s="9"/>
       <c r="C919" s="3"/>
     </row>
     <row r="920">
       <c r="A920" s="3"/>
-      <c r="B920" s="11"/>
+      <c r="B920" s="9"/>
       <c r="C920" s="3"/>
     </row>
     <row r="921">
       <c r="A921" s="3"/>
-      <c r="B921" s="11"/>
+      <c r="B921" s="9"/>
       <c r="C921" s="3"/>
     </row>
     <row r="922">
       <c r="A922" s="3"/>
-      <c r="B922" s="11"/>
+      <c r="B922" s="9"/>
       <c r="C922" s="3"/>
     </row>
     <row r="923">
       <c r="A923" s="3"/>
-      <c r="B923" s="11"/>
+      <c r="B923" s="9"/>
       <c r="C923" s="3"/>
     </row>
     <row r="924">
       <c r="A924" s="3"/>
-      <c r="B924" s="11"/>
+      <c r="B924" s="9"/>
       <c r="C924" s="3"/>
     </row>
     <row r="925">
       <c r="A925" s="3"/>
-      <c r="B925" s="11"/>
+      <c r="B925" s="9"/>
       <c r="C925" s="3"/>
     </row>
     <row r="926">
       <c r="A926" s="3"/>
-      <c r="B926" s="11"/>
+      <c r="B926" s="9"/>
       <c r="C926" s="3"/>
     </row>
     <row r="927">
       <c r="A927" s="3"/>
-      <c r="B927" s="11"/>
+      <c r="B927" s="9"/>
       <c r="C927" s="3"/>
     </row>
     <row r="928">
       <c r="A928" s="3"/>
-      <c r="B928" s="11"/>
+      <c r="B928" s="9"/>
       <c r="C928" s="3"/>
     </row>
     <row r="929">
       <c r="A929" s="3"/>
-      <c r="B929" s="11"/>
+      <c r="B929" s="9"/>
       <c r="C929" s="3"/>
     </row>
     <row r="930">
       <c r="A930" s="3"/>
-      <c r="B930" s="11"/>
+      <c r="B930" s="9"/>
       <c r="C930" s="3"/>
     </row>
     <row r="931">
       <c r="A931" s="3"/>
-      <c r="B931" s="11"/>
+      <c r="B931" s="9"/>
       <c r="C931" s="3"/>
     </row>
     <row r="932">
       <c r="A932" s="3"/>
-      <c r="B932" s="11"/>
+      <c r="B932" s="9"/>
       <c r="C932" s="3"/>
     </row>
     <row r="933">
       <c r="A933" s="3"/>
-      <c r="B933" s="11"/>
+      <c r="B933" s="9"/>
       <c r="C933" s="3"/>
     </row>
     <row r="934">
       <c r="A934" s="3"/>
-      <c r="B934" s="11"/>
+      <c r="B934" s="9"/>
       <c r="C934" s="3"/>
     </row>
     <row r="935">
       <c r="A935" s="3"/>
-      <c r="B935" s="11"/>
+      <c r="B935" s="9"/>
       <c r="C935" s="3"/>
     </row>
     <row r="936">
       <c r="A936" s="3"/>
-      <c r="B936" s="11"/>
+      <c r="B936" s="9"/>
       <c r="C936" s="3"/>
     </row>
     <row r="937">
       <c r="A937" s="3"/>
-      <c r="B937" s="11"/>
+      <c r="B937" s="9"/>
       <c r="C937" s="3"/>
     </row>
     <row r="938">
       <c r="A938" s="3"/>
-      <c r="B938" s="11"/>
+      <c r="B938" s="9"/>
       <c r="C938" s="3"/>
     </row>
     <row r="939">
       <c r="A939" s="3"/>
-      <c r="B939" s="11"/>
+      <c r="B939" s="9"/>
       <c r="C939" s="3"/>
     </row>
     <row r="940">
       <c r="A940" s="3"/>
-      <c r="B940" s="11"/>
+      <c r="B940" s="9"/>
       <c r="C940" s="3"/>
     </row>
     <row r="941">
       <c r="A941" s="3"/>
-      <c r="B941" s="11"/>
+      <c r="B941" s="9"/>
       <c r="C941" s="3"/>
     </row>
     <row r="942">
       <c r="A942" s="3"/>
-      <c r="B942" s="11"/>
+      <c r="B942" s="9"/>
       <c r="C942" s="3"/>
     </row>
     <row r="943">
       <c r="A943" s="3"/>
-      <c r="B943" s="11"/>
+      <c r="B943" s="9"/>
       <c r="C943" s="3"/>
     </row>
     <row r="944">
       <c r="A944" s="3"/>
-      <c r="B944" s="11"/>
+      <c r="B944" s="9"/>
       <c r="C944" s="3"/>
     </row>
     <row r="945">
       <c r="A945" s="3"/>
-      <c r="B945" s="11"/>
+      <c r="B945" s="9"/>
       <c r="C945" s="3"/>
     </row>
     <row r="946">
       <c r="A946" s="3"/>
-      <c r="B946" s="11"/>
+      <c r="B946" s="9"/>
       <c r="C946" s="3"/>
     </row>
     <row r="947">
       <c r="A947" s="3"/>
-      <c r="B947" s="11"/>
+      <c r="B947" s="9"/>
       <c r="C947" s="3"/>
     </row>
     <row r="948">
       <c r="A948" s="3"/>
-      <c r="B948" s="11"/>
+      <c r="B948" s="9"/>
       <c r="C948" s="3"/>
     </row>
     <row r="949">
       <c r="A949" s="3"/>
-      <c r="B949" s="11"/>
+      <c r="B949" s="9"/>
       <c r="C949" s="3"/>
     </row>
     <row r="950">
       <c r="A950" s="3"/>
-      <c r="B950" s="11"/>
+      <c r="B950" s="9"/>
       <c r="C950" s="3"/>
     </row>
     <row r="951">
       <c r="A951" s="3"/>
-      <c r="B951" s="11"/>
+      <c r="B951" s="9"/>
       <c r="C951" s="3"/>
     </row>
     <row r="952">
       <c r="A952" s="3"/>
-      <c r="B952" s="11"/>
+      <c r="B952" s="9"/>
       <c r="C952" s="3"/>
     </row>
     <row r="953">
       <c r="A953" s="3"/>
-      <c r="B953" s="11"/>
+      <c r="B953" s="9"/>
       <c r="C953" s="3"/>
     </row>
     <row r="954">
       <c r="A954" s="3"/>
-      <c r="B954" s="11"/>
+      <c r="B954" s="9"/>
       <c r="C954" s="3"/>
     </row>
     <row r="955">
       <c r="A955" s="3"/>
-      <c r="B955" s="11"/>
+      <c r="B955" s="9"/>
       <c r="C955" s="3"/>
     </row>
     <row r="956">
       <c r="A956" s="3"/>
-      <c r="B956" s="11"/>
+      <c r="B956" s="9"/>
       <c r="C956" s="3"/>
     </row>
     <row r="957">
       <c r="A957" s="3"/>
-      <c r="B957" s="11"/>
+      <c r="B957" s="9"/>
       <c r="C957" s="3"/>
     </row>
     <row r="958">
       <c r="A958" s="3"/>
-      <c r="B958" s="11"/>
+      <c r="B958" s="9"/>
       <c r="C958" s="3"/>
     </row>
     <row r="959">
       <c r="A959" s="3"/>
-      <c r="B959" s="11"/>
+      <c r="B959" s="9"/>
       <c r="C959" s="3"/>
     </row>
     <row r="960">
       <c r="A960" s="3"/>
-      <c r="B960" s="11"/>
+      <c r="B960" s="9"/>
       <c r="C960" s="3"/>
     </row>
     <row r="961">
       <c r="A961" s="3"/>
-      <c r="B961" s="11"/>
+      <c r="B961" s="9"/>
       <c r="C961" s="3"/>
     </row>
     <row r="962">
       <c r="A962" s="3"/>
-      <c r="B962" s="11"/>
+      <c r="B962" s="9"/>
       <c r="C962" s="3"/>
     </row>
     <row r="963">
       <c r="A963" s="3"/>
-      <c r="B963" s="11"/>
+      <c r="B963" s="9"/>
       <c r="C963" s="3"/>
     </row>
     <row r="964">
       <c r="A964" s="3"/>
-      <c r="B964" s="11"/>
+      <c r="B964" s="9"/>
       <c r="C964" s="3"/>
     </row>
     <row r="965">
       <c r="A965" s="3"/>
-      <c r="B965" s="11"/>
+      <c r="B965" s="9"/>
       <c r="C965" s="3"/>
     </row>
     <row r="966">
       <c r="A966" s="3"/>
-      <c r="B966" s="11"/>
+      <c r="B966" s="9"/>
       <c r="C966" s="3"/>
     </row>
     <row r="967">
       <c r="A967" s="3"/>
-      <c r="B967" s="11"/>
+      <c r="B967" s="9"/>
       <c r="C967" s="3"/>
     </row>
     <row r="968">
       <c r="A968" s="3"/>
-      <c r="B968" s="11"/>
+      <c r="B968" s="9"/>
       <c r="C968" s="3"/>
     </row>
     <row r="969">
       <c r="A969" s="3"/>
-      <c r="B969" s="11"/>
+      <c r="B969" s="9"/>
       <c r="C969" s="3"/>
     </row>
     <row r="970">
       <c r="A970" s="3"/>
-      <c r="B970" s="11"/>
+      <c r="B970" s="9"/>
       <c r="C970" s="3"/>
     </row>
     <row r="971">
       <c r="A971" s="3"/>
-      <c r="B971" s="11"/>
+      <c r="B971" s="9"/>
       <c r="C971" s="3"/>
     </row>
     <row r="972">
       <c r="A972" s="3"/>
-      <c r="B972" s="11"/>
+      <c r="B972" s="9"/>
       <c r="C972" s="3"/>
     </row>
     <row r="973">
       <c r="A973" s="3"/>
-      <c r="B973" s="11"/>
+      <c r="B973" s="9"/>
       <c r="C973" s="3"/>
     </row>
     <row r="974">
       <c r="A974" s="3"/>
-      <c r="B974" s="11"/>
+      <c r="B974" s="9"/>
       <c r="C974" s="3"/>
     </row>
     <row r="975">
       <c r="A975" s="3"/>
-      <c r="B975" s="11"/>
+      <c r="B975" s="9"/>
       <c r="C975" s="3"/>
     </row>
     <row r="976">
       <c r="A976" s="3"/>
-      <c r="B976" s="11"/>
+      <c r="B976" s="9"/>
       <c r="C976" s="3"/>
     </row>
     <row r="977">
       <c r="A977" s="3"/>
-      <c r="B977" s="11"/>
+      <c r="B977" s="9"/>
       <c r="C977" s="3"/>
     </row>
     <row r="978">
       <c r="A978" s="3"/>
-      <c r="B978" s="11"/>
+      <c r="B978" s="9"/>
       <c r="C978" s="3"/>
     </row>
     <row r="979">
       <c r="A979" s="3"/>
-      <c r="B979" s="11"/>
+      <c r="B979" s="9"/>
       <c r="C979" s="3"/>
     </row>
     <row r="980">
       <c r="A980" s="3"/>
-      <c r="B980" s="11"/>
+      <c r="B980" s="9"/>
       <c r="C980" s="3"/>
     </row>
     <row r="981">
       <c r="A981" s="3"/>
-      <c r="B981" s="11"/>
+      <c r="B981" s="9"/>
       <c r="C981" s="3"/>
     </row>
     <row r="982">
       <c r="A982" s="3"/>
-      <c r="B982" s="11"/>
+      <c r="B982" s="9"/>
       <c r="C982" s="3"/>
     </row>
     <row r="983">
       <c r="A983" s="3"/>
-      <c r="B983" s="11"/>
+      <c r="B983" s="9"/>
       <c r="C983" s="3"/>
     </row>
     <row r="984">
       <c r="A984" s="3"/>
-      <c r="B984" s="11"/>
+      <c r="B984" s="9"/>
       <c r="C984" s="3"/>
     </row>
     <row r="985">
       <c r="A985" s="3"/>
-      <c r="B985" s="11"/>
+      <c r="B985" s="9"/>
       <c r="C985" s="3"/>
     </row>
     <row r="986">
       <c r="A986" s="3"/>
-      <c r="B986" s="11"/>
+      <c r="B986" s="9"/>
       <c r="C986" s="3"/>
     </row>
     <row r="987">
       <c r="A987" s="3"/>
-      <c r="B987" s="11"/>
+      <c r="B987" s="9"/>
       <c r="C987" s="3"/>
     </row>
     <row r="988">
       <c r="A988" s="3"/>
-      <c r="B988" s="11"/>
+      <c r="B988" s="9"/>
       <c r="C988" s="3"/>
     </row>
     <row r="989">
       <c r="A989" s="3"/>
-      <c r="B989" s="11"/>
+      <c r="B989" s="9"/>
       <c r="C989" s="3"/>
     </row>
     <row r="990">
       <c r="A990" s="3"/>
-      <c r="B990" s="11"/>
+      <c r="B990" s="9"/>
       <c r="C990" s="3"/>
     </row>
     <row r="991">
       <c r="A991" s="3"/>
-      <c r="B991" s="11"/>
+      <c r="B991" s="9"/>
       <c r="C991" s="3"/>
     </row>
     <row r="992">
       <c r="A992" s="3"/>
-      <c r="B992" s="11"/>
+      <c r="B992" s="9"/>
       <c r="C992" s="3"/>
     </row>
     <row r="993">
       <c r="A993" s="3"/>
-      <c r="B993" s="11"/>
+      <c r="B993" s="9"/>
       <c r="C993" s="3"/>
     </row>
     <row r="994">
       <c r="A994" s="3"/>
-      <c r="B994" s="11"/>
+      <c r="B994" s="9"/>
       <c r="C994" s="3"/>
     </row>
     <row r="995">
       <c r="A995" s="3"/>
-      <c r="B995" s="11"/>
+      <c r="B995" s="9"/>
       <c r="C995" s="3"/>
     </row>
   </sheetData>
